--- a/template/26-A-0001 견적서(일반면적)_에이스방재_양식.xlsx
+++ b/template/26-A-0001 견적서(일반면적)_에이스방재_양식.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="현재_통합_문서"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Master\Documents\Project\견적서 자동화 프로젝트\기계사업부\template\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="c:\Users\Master\Documents\Project\견적서 자동화 프로젝트\기계사업부\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3996A188-BCE8-4695-8722-2A471E967281}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1451F768-7A49-4CFA-A335-EE9697B3ABC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="874" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9690" yWindow="7290" windowWidth="7500" windowHeight="6000" tabRatio="874" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VXXXXX" sheetId="6" state="veryHidden" r:id="rId1"/>
@@ -6751,141 +6751,61 @@
     <xf numFmtId="0" fontId="144" fillId="0" borderId="87" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="124" fillId="0" borderId="80" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="124" fillId="0" borderId="81" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="124" fillId="0" borderId="82" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="128" fillId="0" borderId="83" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="128" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="181" fontId="123" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="117" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="117" fillId="36" borderId="75" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="124" fillId="0" borderId="77" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="124" fillId="0" borderId="75" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="31" fontId="136" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="123" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="150" fillId="0" borderId="95" xfId="1442" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="150" fillId="0" borderId="0" xfId="1442" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="150" fillId="0" borderId="92" xfId="1442" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="125" fillId="0" borderId="100" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="125" fillId="0" borderId="98" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="125" fillId="0" borderId="102" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="117" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="124" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="117" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="124" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="234" fontId="118" fillId="31" borderId="47" xfId="1267" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="117" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="116" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="125" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="117" fillId="36" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="124" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="124" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="181" fontId="117" fillId="0" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="126" fillId="35" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="126" fillId="35" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="126" fillId="35" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="117" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="126" fillId="35" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="117" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="31" fontId="123" fillId="0" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="116" fillId="36" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="116" fillId="36" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="116" fillId="36" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="125" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="125" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="125" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="116" fillId="36" borderId="97" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="116" fillId="36" borderId="98" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="116" fillId="36" borderId="99" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="125" fillId="0" borderId="100" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="125" fillId="0" borderId="98" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="125" fillId="0" borderId="102" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="117" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="117" fillId="0" borderId="70" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="117" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="118" fillId="33" borderId="76" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="118" fillId="33" borderId="77" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="118" fillId="33" borderId="75" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="137" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="140" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="140" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="41" fontId="140" fillId="0" borderId="0" xfId="1267" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="117" fillId="0" borderId="69" xfId="1267" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="117" fillId="0" borderId="70" xfId="1267" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="112" fillId="35" borderId="78" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="112" fillId="35" borderId="91" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="112" fillId="35" borderId="79" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="123" fillId="0" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="117" fillId="0" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="117" fillId="0" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="123" fillId="0" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
@@ -6896,145 +6816,19 @@
     <xf numFmtId="178" fontId="117" fillId="0" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="178" fontId="117" fillId="0" borderId="69" xfId="1267" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="117" fillId="0" borderId="52" xfId="1267" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="178" fontId="117" fillId="0" borderId="70" xfId="1267" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="117" fillId="0" borderId="51" xfId="1267" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="112" fillId="35" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="112" fillId="35" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="112" fillId="35" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="113" fillId="0" borderId="68" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="113" fillId="0" borderId="69" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="113" fillId="0" borderId="70" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="113" fillId="0" borderId="78" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="113" fillId="0" borderId="91" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="113" fillId="0" borderId="79" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="118" fillId="36" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="118" fillId="36" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="118" fillId="36" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="52" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="51" xfId="0" applyBorder="1"/>
-    <xf numFmtId="178" fontId="118" fillId="36" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="52" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="51" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="123" fillId="0" borderId="68" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="117" fillId="0" borderId="69" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="117" fillId="0" borderId="70" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="118" fillId="36" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="117" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="117" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="117" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="126" fillId="35" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="126" fillId="35" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="149" fillId="35" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="126" fillId="35" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="117" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="117" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="117" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="127" fillId="0" borderId="83" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="127" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="133" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="116" fillId="36" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="116" fillId="36" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="116" fillId="36" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="125" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="125" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="125" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="131" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="131" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="116" fillId="36" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="114" fillId="0" borderId="104" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="115" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="124" fillId="0" borderId="84" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="116" fillId="36" borderId="101" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="116" fillId="36" borderId="98" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="116" fillId="36" borderId="99" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="125" fillId="0" borderId="100" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -7051,6 +6845,27 @@
     </xf>
     <xf numFmtId="0" fontId="116" fillId="36" borderId="103" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="116" fillId="36" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="116" fillId="36" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="116" fillId="36" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="117" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="117" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="117" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="116" fillId="36" borderId="97" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="116" fillId="36" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -7081,55 +6896,243 @@
     <xf numFmtId="0" fontId="119" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="116" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="125" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="117" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="117" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="117" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="31" fontId="123" fillId="0" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="117" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="117" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="116" fillId="36" borderId="111" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="124" fillId="0" borderId="112" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="124" fillId="0" borderId="113" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="150" fillId="0" borderId="95" xfId="1442" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="150" fillId="0" borderId="0" xfId="1442" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="150" fillId="0" borderId="92" xfId="1442" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="117" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="117" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="125" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="125" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="127" fillId="0" borderId="83" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="127" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="133" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="116" fillId="36" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="116" fillId="36" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="116" fillId="36" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="125" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="125" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="125" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="131" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="131" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="116" fillId="36" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="125" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="114" fillId="0" borderId="104" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="234" fontId="118" fillId="31" borderId="47" xfId="1267" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="115" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="124" fillId="0" borderId="84" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="126" fillId="35" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="126" fillId="35" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="149" fillId="35" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="117" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="126" fillId="35" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="126" fillId="35" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="126" fillId="35" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="52" xfId="0" applyBorder="1"/>
+    <xf numFmtId="178" fontId="126" fillId="35" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="123" fillId="0" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="117" fillId="0" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="117" fillId="0" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="117" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="117" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="117" fillId="0" borderId="70" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="117" fillId="0" borderId="69" xfId="1267" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="117" fillId="0" borderId="70" xfId="1267" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="112" fillId="35" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="112" fillId="35" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="112" fillId="35" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="112" fillId="35" borderId="78" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="112" fillId="35" borderId="91" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="112" fillId="35" borderId="79" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="113" fillId="0" borderId="68" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="113" fillId="0" borderId="69" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="113" fillId="0" borderId="70" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="113" fillId="0" borderId="78" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="113" fillId="0" borderId="91" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="113" fillId="0" borderId="79" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="118" fillId="36" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="118" fillId="36" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="118" fillId="36" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="51" xfId="0" applyBorder="1"/>
+    <xf numFmtId="178" fontId="118" fillId="36" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="52" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="51" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="123" fillId="0" borderId="68" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="117" fillId="0" borderId="69" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="117" fillId="0" borderId="70" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="118" fillId="36" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="118" fillId="33" borderId="76" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="118" fillId="33" borderId="77" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="118" fillId="33" borderId="75" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="137" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="140" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="140" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="140" fillId="0" borderId="0" xfId="1267" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="117" fillId="0" borderId="69" xfId="1267" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="117" fillId="0" borderId="70" xfId="1267" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="124" fillId="0" borderId="80" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="124" fillId="0" borderId="81" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="124" fillId="0" borderId="82" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="128" fillId="0" borderId="83" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="128" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="181" fontId="123" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="117" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="117" fillId="36" borderId="75" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="126" fillId="35" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="124" fillId="0" borderId="77" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="124" fillId="0" borderId="75" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="31" fontId="136" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="117" fillId="0" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="117" fillId="0" borderId="52" xfId="1267" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="117" fillId="0" borderId="51" xfId="1267" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="101" fillId="30" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -7158,6 +7161,12 @@
     <xf numFmtId="0" fontId="105" fillId="30" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="99" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="97" fillId="0" borderId="79" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="97" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -7179,10 +7188,10 @@
     <xf numFmtId="0" fontId="97" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="99" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="97" fillId="0" borderId="79" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="98" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="97" fillId="0" borderId="89" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="111" fillId="33" borderId="69" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -7206,12 +7215,6 @@
     <xf numFmtId="0" fontId="98" fillId="37" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="98" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="97" fillId="0" borderId="89" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -7232,9 +7235,6 @@
     </xf>
     <xf numFmtId="2" fontId="68" fillId="31" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="123" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1469">
@@ -10133,6 +10133,9 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:AB37"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
@@ -10151,129 +10154,129 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="33.75" customHeight="1">
-      <c r="A1" s="171"/>
-      <c r="B1" s="172"/>
-      <c r="C1" s="172"/>
-      <c r="D1" s="172"/>
-      <c r="E1" s="172"/>
-      <c r="F1" s="172"/>
-      <c r="G1" s="172"/>
-      <c r="H1" s="172"/>
-      <c r="I1" s="172"/>
-      <c r="J1" s="172"/>
-      <c r="K1" s="172"/>
-      <c r="L1" s="172"/>
-      <c r="M1" s="172"/>
-      <c r="N1" s="172"/>
-      <c r="O1" s="172"/>
-      <c r="P1" s="172"/>
-      <c r="Q1" s="172"/>
-      <c r="R1" s="172"/>
-      <c r="S1" s="172"/>
-      <c r="T1" s="172"/>
-      <c r="U1" s="172"/>
-      <c r="V1" s="172"/>
-      <c r="W1" s="172"/>
-      <c r="X1" s="172"/>
-      <c r="Y1" s="172"/>
-      <c r="Z1" s="172"/>
-      <c r="AA1" s="172"/>
-      <c r="AB1" s="173"/>
+      <c r="A1" s="294"/>
+      <c r="B1" s="295"/>
+      <c r="C1" s="295"/>
+      <c r="D1" s="295"/>
+      <c r="E1" s="295"/>
+      <c r="F1" s="295"/>
+      <c r="G1" s="295"/>
+      <c r="H1" s="295"/>
+      <c r="I1" s="295"/>
+      <c r="J1" s="295"/>
+      <c r="K1" s="295"/>
+      <c r="L1" s="295"/>
+      <c r="M1" s="295"/>
+      <c r="N1" s="295"/>
+      <c r="O1" s="295"/>
+      <c r="P1" s="295"/>
+      <c r="Q1" s="295"/>
+      <c r="R1" s="295"/>
+      <c r="S1" s="295"/>
+      <c r="T1" s="295"/>
+      <c r="U1" s="295"/>
+      <c r="V1" s="295"/>
+      <c r="W1" s="295"/>
+      <c r="X1" s="295"/>
+      <c r="Y1" s="295"/>
+      <c r="Z1" s="295"/>
+      <c r="AA1" s="295"/>
+      <c r="AB1" s="296"/>
     </row>
     <row r="2" spans="1:28" s="106" customFormat="1" ht="48.75">
-      <c r="A2" s="255" t="s">
+      <c r="A2" s="233" t="s">
         <v>140</v>
       </c>
-      <c r="B2" s="256"/>
-      <c r="C2" s="256"/>
-      <c r="D2" s="256"/>
-      <c r="E2" s="256"/>
-      <c r="F2" s="256"/>
-      <c r="G2" s="256"/>
-      <c r="H2" s="256"/>
-      <c r="I2" s="256"/>
-      <c r="J2" s="256"/>
-      <c r="K2" s="256"/>
-      <c r="L2" s="256"/>
-      <c r="M2" s="256"/>
-      <c r="N2" s="256"/>
-      <c r="O2" s="256"/>
-      <c r="P2" s="256"/>
-      <c r="Q2" s="256"/>
-      <c r="R2" s="256"/>
-      <c r="S2" s="256"/>
-      <c r="T2" s="256"/>
-      <c r="U2" s="256"/>
-      <c r="V2" s="256"/>
-      <c r="W2" s="256"/>
-      <c r="X2" s="256"/>
-      <c r="Y2" s="256"/>
-      <c r="Z2" s="256"/>
-      <c r="AA2" s="256"/>
+      <c r="B2" s="234"/>
+      <c r="C2" s="234"/>
+      <c r="D2" s="234"/>
+      <c r="E2" s="234"/>
+      <c r="F2" s="234"/>
+      <c r="G2" s="234"/>
+      <c r="H2" s="234"/>
+      <c r="I2" s="234"/>
+      <c r="J2" s="234"/>
+      <c r="K2" s="234"/>
+      <c r="L2" s="234"/>
+      <c r="M2" s="234"/>
+      <c r="N2" s="234"/>
+      <c r="O2" s="234"/>
+      <c r="P2" s="234"/>
+      <c r="Q2" s="234"/>
+      <c r="R2" s="234"/>
+      <c r="S2" s="234"/>
+      <c r="T2" s="234"/>
+      <c r="U2" s="234"/>
+      <c r="V2" s="234"/>
+      <c r="W2" s="234"/>
+      <c r="X2" s="234"/>
+      <c r="Y2" s="234"/>
+      <c r="Z2" s="234"/>
+      <c r="AA2" s="234"/>
       <c r="AB2" s="114"/>
     </row>
     <row r="3" spans="1:28" s="106" customFormat="1" ht="39.75" customHeight="1">
-      <c r="A3" s="267" t="s">
+      <c r="A3" s="246" t="s">
         <v>197</v>
       </c>
-      <c r="B3" s="268"/>
-      <c r="C3" s="268"/>
-      <c r="D3" s="268"/>
-      <c r="E3" s="268"/>
-      <c r="F3" s="268"/>
-      <c r="G3" s="268"/>
-      <c r="H3" s="268"/>
-      <c r="I3" s="268"/>
-      <c r="J3" s="268"/>
-      <c r="K3" s="268"/>
-      <c r="L3" s="268"/>
-      <c r="M3" s="268"/>
-      <c r="N3" s="268"/>
-      <c r="O3" s="268"/>
-      <c r="P3" s="268"/>
-      <c r="Q3" s="268"/>
-      <c r="R3" s="268"/>
-      <c r="S3" s="268"/>
-      <c r="T3" s="268"/>
-      <c r="U3" s="268"/>
-      <c r="V3" s="268"/>
-      <c r="W3" s="268"/>
-      <c r="X3" s="268"/>
-      <c r="Y3" s="268"/>
-      <c r="Z3" s="268"/>
-      <c r="AA3" s="268"/>
-      <c r="AB3" s="269"/>
+      <c r="B3" s="247"/>
+      <c r="C3" s="247"/>
+      <c r="D3" s="247"/>
+      <c r="E3" s="247"/>
+      <c r="F3" s="247"/>
+      <c r="G3" s="247"/>
+      <c r="H3" s="247"/>
+      <c r="I3" s="247"/>
+      <c r="J3" s="247"/>
+      <c r="K3" s="247"/>
+      <c r="L3" s="247"/>
+      <c r="M3" s="247"/>
+      <c r="N3" s="247"/>
+      <c r="O3" s="247"/>
+      <c r="P3" s="247"/>
+      <c r="Q3" s="247"/>
+      <c r="R3" s="247"/>
+      <c r="S3" s="247"/>
+      <c r="T3" s="247"/>
+      <c r="U3" s="247"/>
+      <c r="V3" s="247"/>
+      <c r="W3" s="247"/>
+      <c r="X3" s="247"/>
+      <c r="Y3" s="247"/>
+      <c r="Z3" s="247"/>
+      <c r="AA3" s="247"/>
+      <c r="AB3" s="248"/>
     </row>
     <row r="4" spans="1:28" s="106" customFormat="1" ht="39.75" customHeight="1">
-      <c r="A4" s="174" t="s">
+      <c r="A4" s="297" t="s">
         <v>160</v>
       </c>
-      <c r="B4" s="175"/>
-      <c r="C4" s="175"/>
-      <c r="D4" s="175"/>
-      <c r="E4" s="175"/>
-      <c r="F4" s="175"/>
-      <c r="G4" s="175"/>
-      <c r="H4" s="175"/>
-      <c r="I4" s="175"/>
-      <c r="J4" s="175"/>
-      <c r="K4" s="175"/>
-      <c r="L4" s="175"/>
-      <c r="M4" s="175"/>
-      <c r="N4" s="175"/>
-      <c r="O4" s="175"/>
-      <c r="P4" s="175"/>
-      <c r="Q4" s="175"/>
-      <c r="R4" s="175"/>
-      <c r="S4" s="175"/>
-      <c r="T4" s="175"/>
-      <c r="U4" s="175"/>
-      <c r="V4" s="175"/>
-      <c r="W4" s="175"/>
-      <c r="X4" s="175"/>
-      <c r="Y4" s="175"/>
-      <c r="Z4" s="175"/>
-      <c r="AA4" s="175"/>
+      <c r="B4" s="298"/>
+      <c r="C4" s="298"/>
+      <c r="D4" s="298"/>
+      <c r="E4" s="298"/>
+      <c r="F4" s="298"/>
+      <c r="G4" s="298"/>
+      <c r="H4" s="298"/>
+      <c r="I4" s="298"/>
+      <c r="J4" s="298"/>
+      <c r="K4" s="298"/>
+      <c r="L4" s="298"/>
+      <c r="M4" s="298"/>
+      <c r="N4" s="298"/>
+      <c r="O4" s="298"/>
+      <c r="P4" s="298"/>
+      <c r="Q4" s="298"/>
+      <c r="R4" s="298"/>
+      <c r="S4" s="298"/>
+      <c r="T4" s="298"/>
+      <c r="U4" s="298"/>
+      <c r="V4" s="298"/>
+      <c r="W4" s="298"/>
+      <c r="X4" s="298"/>
+      <c r="Y4" s="298"/>
+      <c r="Z4" s="298"/>
+      <c r="AA4" s="298"/>
       <c r="AB4" s="115"/>
     </row>
     <row r="5" spans="1:28" s="106" customFormat="1" ht="20.100000000000001" customHeight="1">
@@ -10288,15 +10291,15 @@
       <c r="J5" s="117"/>
       <c r="K5" s="117"/>
       <c r="L5" s="117"/>
-      <c r="M5" s="264" t="s">
+      <c r="M5" s="242" t="s">
         <v>171</v>
       </c>
-      <c r="N5" s="264"/>
-      <c r="O5" s="264"/>
-      <c r="P5" s="264"/>
-      <c r="Q5" s="264"/>
-      <c r="R5" s="264"/>
-      <c r="S5" s="264"/>
+      <c r="N5" s="242"/>
+      <c r="O5" s="242"/>
+      <c r="P5" s="242"/>
+      <c r="Q5" s="242"/>
+      <c r="R5" s="242"/>
+      <c r="S5" s="242"/>
       <c r="T5" s="117"/>
       <c r="U5" s="117"/>
       <c r="V5" s="117"/>
@@ -10319,21 +10322,21 @@
       <c r="J6" s="113"/>
       <c r="K6" s="113"/>
       <c r="L6" s="113"/>
-      <c r="M6" s="265"/>
-      <c r="N6" s="265"/>
-      <c r="O6" s="265"/>
-      <c r="P6" s="265"/>
-      <c r="Q6" s="265"/>
-      <c r="R6" s="265"/>
-      <c r="S6" s="265"/>
+      <c r="M6" s="243"/>
+      <c r="N6" s="243"/>
+      <c r="O6" s="243"/>
+      <c r="P6" s="243"/>
+      <c r="Q6" s="243"/>
+      <c r="R6" s="243"/>
+      <c r="S6" s="243"/>
       <c r="T6" s="113"/>
       <c r="U6" s="113"/>
       <c r="V6" s="113"/>
-      <c r="W6" s="257"/>
-      <c r="X6" s="257"/>
-      <c r="Y6" s="257"/>
-      <c r="Z6" s="257"/>
-      <c r="AA6" s="257"/>
+      <c r="W6" s="235"/>
+      <c r="X6" s="235"/>
+      <c r="Y6" s="235"/>
+      <c r="Z6" s="235"/>
+      <c r="AA6" s="235"/>
       <c r="AB6" s="114"/>
     </row>
     <row r="7" spans="1:28" s="106" customFormat="1" ht="32.1" customHeight="1">
@@ -10343,37 +10346,37 @@
         <v>152</v>
       </c>
       <c r="D7" s="107"/>
-      <c r="E7" s="176" t="s">
+      <c r="E7" s="299" t="s">
         <v>184</v>
       </c>
-      <c r="F7" s="177"/>
-      <c r="G7" s="177"/>
-      <c r="H7" s="177"/>
-      <c r="I7" s="177"/>
-      <c r="J7" s="177"/>
+      <c r="F7" s="300"/>
+      <c r="G7" s="300"/>
+      <c r="H7" s="300"/>
+      <c r="I7" s="300"/>
+      <c r="J7" s="300"/>
       <c r="K7" s="107"/>
       <c r="L7" s="121"/>
-      <c r="M7" s="273" t="s">
+      <c r="M7" s="201" t="s">
         <v>115</v>
       </c>
-      <c r="N7" s="258" t="s">
+      <c r="N7" s="236" t="s">
         <v>116</v>
       </c>
-      <c r="O7" s="259"/>
-      <c r="P7" s="260"/>
-      <c r="Q7" s="261" t="s">
+      <c r="O7" s="237"/>
+      <c r="P7" s="238"/>
+      <c r="Q7" s="239" t="s">
         <v>139</v>
       </c>
-      <c r="R7" s="262"/>
-      <c r="S7" s="262"/>
-      <c r="T7" s="262"/>
-      <c r="U7" s="262"/>
-      <c r="V7" s="262"/>
-      <c r="W7" s="262"/>
-      <c r="X7" s="262"/>
-      <c r="Y7" s="262"/>
-      <c r="Z7" s="262"/>
-      <c r="AA7" s="263"/>
+      <c r="R7" s="240"/>
+      <c r="S7" s="240"/>
+      <c r="T7" s="240"/>
+      <c r="U7" s="240"/>
+      <c r="V7" s="240"/>
+      <c r="W7" s="240"/>
+      <c r="X7" s="240"/>
+      <c r="Y7" s="240"/>
+      <c r="Z7" s="240"/>
+      <c r="AA7" s="241"/>
       <c r="AB7" s="114"/>
     </row>
     <row r="8" spans="1:28" s="106" customFormat="1" ht="32.1" customHeight="1">
@@ -10383,39 +10386,39 @@
         <v>151</v>
       </c>
       <c r="D8" s="107"/>
-      <c r="E8" s="339" t="s">
+      <c r="E8" s="171" t="s">
         <v>183</v>
       </c>
-      <c r="F8" s="339"/>
-      <c r="G8" s="339"/>
-      <c r="H8" s="339"/>
-      <c r="I8" s="339"/>
+      <c r="F8" s="171"/>
+      <c r="G8" s="171"/>
+      <c r="H8" s="171"/>
+      <c r="I8" s="171"/>
       <c r="J8" s="107"/>
       <c r="K8" s="107"/>
       <c r="L8" s="121"/>
-      <c r="M8" s="274"/>
-      <c r="N8" s="189" t="s">
+      <c r="M8" s="202"/>
+      <c r="N8" s="204" t="s">
         <v>107</v>
       </c>
-      <c r="O8" s="190"/>
-      <c r="P8" s="191"/>
-      <c r="Q8" s="192" t="s">
+      <c r="O8" s="205"/>
+      <c r="P8" s="206"/>
+      <c r="Q8" s="231" t="s">
         <v>108</v>
       </c>
-      <c r="R8" s="193"/>
-      <c r="S8" s="193"/>
-      <c r="T8" s="193"/>
-      <c r="U8" s="266" t="s">
+      <c r="R8" s="232"/>
+      <c r="S8" s="232"/>
+      <c r="T8" s="232"/>
+      <c r="U8" s="244" t="s">
         <v>109</v>
       </c>
-      <c r="V8" s="190"/>
-      <c r="W8" s="191"/>
-      <c r="X8" s="192" t="s">
+      <c r="V8" s="205"/>
+      <c r="W8" s="206"/>
+      <c r="X8" s="231" t="s">
         <v>110</v>
       </c>
-      <c r="Y8" s="193"/>
-      <c r="Z8" s="193"/>
-      <c r="AA8" s="194"/>
+      <c r="Y8" s="232"/>
+      <c r="Z8" s="232"/>
+      <c r="AA8" s="245"/>
       <c r="AB8" s="114"/>
     </row>
     <row r="9" spans="1:28" s="106" customFormat="1" ht="32.1" customHeight="1">
@@ -10435,25 +10438,25 @@
       <c r="J9" s="108"/>
       <c r="K9" s="108"/>
       <c r="L9" s="122"/>
-      <c r="M9" s="274"/>
-      <c r="N9" s="189" t="s">
+      <c r="M9" s="202"/>
+      <c r="N9" s="204" t="s">
         <v>112</v>
       </c>
-      <c r="O9" s="190"/>
-      <c r="P9" s="191"/>
-      <c r="Q9" s="192" t="s">
+      <c r="O9" s="205"/>
+      <c r="P9" s="206"/>
+      <c r="Q9" s="231" t="s">
         <v>159</v>
       </c>
-      <c r="R9" s="193"/>
-      <c r="S9" s="193"/>
-      <c r="T9" s="193"/>
-      <c r="U9" s="193"/>
-      <c r="V9" s="193"/>
-      <c r="W9" s="193"/>
-      <c r="X9" s="193"/>
-      <c r="Y9" s="193"/>
-      <c r="Z9" s="193"/>
-      <c r="AA9" s="194"/>
+      <c r="R9" s="232"/>
+      <c r="S9" s="232"/>
+      <c r="T9" s="232"/>
+      <c r="U9" s="232"/>
+      <c r="V9" s="232"/>
+      <c r="W9" s="232"/>
+      <c r="X9" s="232"/>
+      <c r="Y9" s="232"/>
+      <c r="Z9" s="232"/>
+      <c r="AA9" s="245"/>
       <c r="AB9" s="114"/>
     </row>
     <row r="10" spans="1:28" s="106" customFormat="1" ht="32.1" customHeight="1">
@@ -10473,29 +10476,29 @@
       <c r="J10" s="107"/>
       <c r="K10" s="107"/>
       <c r="L10" s="107"/>
-      <c r="M10" s="274"/>
-      <c r="N10" s="195" t="s">
+      <c r="M10" s="202"/>
+      <c r="N10" s="210" t="s">
         <v>113</v>
       </c>
-      <c r="O10" s="196"/>
-      <c r="P10" s="197"/>
-      <c r="Q10" s="271" t="s">
+      <c r="O10" s="197"/>
+      <c r="P10" s="198"/>
+      <c r="Q10" s="199" t="s">
         <v>114</v>
       </c>
-      <c r="R10" s="272"/>
-      <c r="S10" s="272"/>
-      <c r="T10" s="272"/>
-      <c r="U10" s="270" t="s">
+      <c r="R10" s="200"/>
+      <c r="S10" s="200"/>
+      <c r="T10" s="200"/>
+      <c r="U10" s="196" t="s">
         <v>100</v>
       </c>
-      <c r="V10" s="196"/>
-      <c r="W10" s="197"/>
-      <c r="X10" s="198" t="s">
+      <c r="V10" s="197"/>
+      <c r="W10" s="198"/>
+      <c r="X10" s="175" t="s">
         <v>118</v>
       </c>
-      <c r="Y10" s="199"/>
-      <c r="Z10" s="199"/>
-      <c r="AA10" s="200"/>
+      <c r="Y10" s="176"/>
+      <c r="Z10" s="176"/>
+      <c r="AA10" s="177"/>
       <c r="AB10" s="114"/>
     </row>
     <row r="11" spans="1:28" s="106" customFormat="1" ht="32.1" customHeight="1">
@@ -10511,29 +10514,29 @@
       <c r="J11" s="107"/>
       <c r="K11" s="107"/>
       <c r="L11" s="107"/>
-      <c r="M11" s="274"/>
-      <c r="N11" s="195" t="s">
+      <c r="M11" s="202"/>
+      <c r="N11" s="210" t="s">
         <v>164</v>
       </c>
-      <c r="O11" s="196"/>
-      <c r="P11" s="197"/>
-      <c r="Q11" s="271" t="s">
+      <c r="O11" s="197"/>
+      <c r="P11" s="198"/>
+      <c r="Q11" s="199" t="s">
         <v>198</v>
       </c>
-      <c r="R11" s="272"/>
-      <c r="S11" s="272"/>
-      <c r="T11" s="279"/>
-      <c r="U11" s="283" t="s">
+      <c r="R11" s="200"/>
+      <c r="S11" s="200"/>
+      <c r="T11" s="214"/>
+      <c r="U11" s="218" t="s">
         <v>199</v>
       </c>
-      <c r="V11" s="284"/>
-      <c r="W11" s="285"/>
-      <c r="X11" s="198" t="s">
+      <c r="V11" s="219"/>
+      <c r="W11" s="220"/>
+      <c r="X11" s="175" t="s">
         <v>201</v>
       </c>
-      <c r="Y11" s="199"/>
-      <c r="Z11" s="199"/>
-      <c r="AA11" s="200"/>
+      <c r="Y11" s="176"/>
+      <c r="Z11" s="176"/>
+      <c r="AA11" s="177"/>
       <c r="AB11" s="114"/>
     </row>
     <row r="12" spans="1:28" s="106" customFormat="1" ht="32.1" customHeight="1" thickBot="1">
@@ -10544,32 +10547,32 @@
       <c r="C12" s="123"/>
       <c r="D12" s="124"/>
       <c r="E12" s="124"/>
-      <c r="F12" s="181"/>
-      <c r="G12" s="181"/>
-      <c r="H12" s="181"/>
-      <c r="I12" s="181"/>
-      <c r="J12" s="181"/>
+      <c r="F12" s="304"/>
+      <c r="G12" s="304"/>
+      <c r="H12" s="304"/>
+      <c r="I12" s="304"/>
+      <c r="J12" s="304"/>
       <c r="K12" s="125"/>
       <c r="L12" s="126"/>
-      <c r="M12" s="275"/>
-      <c r="N12" s="276"/>
-      <c r="O12" s="277"/>
-      <c r="P12" s="278"/>
-      <c r="Q12" s="280"/>
-      <c r="R12" s="281"/>
-      <c r="S12" s="281"/>
-      <c r="T12" s="282"/>
-      <c r="U12" s="289" t="s">
+      <c r="M12" s="203"/>
+      <c r="N12" s="211"/>
+      <c r="O12" s="212"/>
+      <c r="P12" s="213"/>
+      <c r="Q12" s="215"/>
+      <c r="R12" s="216"/>
+      <c r="S12" s="216"/>
+      <c r="T12" s="217"/>
+      <c r="U12" s="228" t="s">
         <v>200</v>
       </c>
-      <c r="V12" s="290"/>
-      <c r="W12" s="291"/>
-      <c r="X12" s="198" t="s">
+      <c r="V12" s="229"/>
+      <c r="W12" s="230"/>
+      <c r="X12" s="175" t="s">
         <v>202</v>
       </c>
-      <c r="Y12" s="199"/>
-      <c r="Z12" s="199"/>
-      <c r="AA12" s="200"/>
+      <c r="Y12" s="176"/>
+      <c r="Z12" s="176"/>
+      <c r="AA12" s="177"/>
       <c r="AB12" s="114"/>
     </row>
     <row r="13" spans="1:28" s="106" customFormat="1" ht="20.100000000000001" customHeight="1">
@@ -10580,166 +10583,166 @@
       <c r="C13" s="123"/>
       <c r="D13" s="124"/>
       <c r="E13" s="124"/>
-      <c r="F13" s="181"/>
-      <c r="G13" s="181"/>
-      <c r="H13" s="181"/>
-      <c r="I13" s="181"/>
-      <c r="J13" s="181"/>
+      <c r="F13" s="304"/>
+      <c r="G13" s="304"/>
+      <c r="H13" s="304"/>
+      <c r="I13" s="304"/>
+      <c r="J13" s="304"/>
       <c r="K13" s="125"/>
       <c r="L13" s="125"/>
       <c r="M13" s="127"/>
-      <c r="N13" s="287"/>
-      <c r="O13" s="287"/>
-      <c r="P13" s="287"/>
-      <c r="Q13" s="288"/>
-      <c r="R13" s="288"/>
-      <c r="S13" s="288"/>
-      <c r="T13" s="288"/>
-      <c r="U13" s="287"/>
-      <c r="V13" s="287"/>
-      <c r="W13" s="287"/>
-      <c r="X13" s="288"/>
-      <c r="Y13" s="288"/>
-      <c r="Z13" s="288"/>
-      <c r="AA13" s="288"/>
+      <c r="N13" s="184"/>
+      <c r="O13" s="184"/>
+      <c r="P13" s="184"/>
+      <c r="Q13" s="185"/>
+      <c r="R13" s="185"/>
+      <c r="S13" s="185"/>
+      <c r="T13" s="185"/>
+      <c r="U13" s="184"/>
+      <c r="V13" s="184"/>
+      <c r="W13" s="184"/>
+      <c r="X13" s="185"/>
+      <c r="Y13" s="185"/>
+      <c r="Z13" s="185"/>
+      <c r="AA13" s="185"/>
       <c r="AB13" s="114"/>
     </row>
     <row r="14" spans="1:28" s="106" customFormat="1" ht="35.1" customHeight="1">
       <c r="A14" s="116"/>
       <c r="B14" s="128"/>
       <c r="C14" s="129"/>
-      <c r="D14" s="182" t="s">
+      <c r="D14" s="186" t="s">
         <v>242</v>
       </c>
-      <c r="E14" s="183"/>
-      <c r="F14" s="183"/>
-      <c r="G14" s="183"/>
-      <c r="H14" s="184"/>
+      <c r="E14" s="179"/>
+      <c r="F14" s="179"/>
+      <c r="G14" s="179"/>
+      <c r="H14" s="181"/>
       <c r="I14" s="100"/>
-      <c r="J14" s="185" t="s">
+      <c r="J14" s="305" t="s">
         <v>183</v>
       </c>
-      <c r="K14" s="186"/>
-      <c r="L14" s="186"/>
-      <c r="M14" s="186"/>
-      <c r="N14" s="186"/>
-      <c r="O14" s="186"/>
-      <c r="P14" s="186"/>
-      <c r="Q14" s="186"/>
-      <c r="R14" s="186"/>
-      <c r="S14" s="186"/>
-      <c r="T14" s="186"/>
-      <c r="U14" s="186"/>
-      <c r="V14" s="186"/>
-      <c r="W14" s="186"/>
-      <c r="X14" s="186"/>
-      <c r="Y14" s="186"/>
-      <c r="Z14" s="186"/>
-      <c r="AA14" s="187"/>
+      <c r="K14" s="226"/>
+      <c r="L14" s="226"/>
+      <c r="M14" s="226"/>
+      <c r="N14" s="226"/>
+      <c r="O14" s="226"/>
+      <c r="P14" s="226"/>
+      <c r="Q14" s="226"/>
+      <c r="R14" s="226"/>
+      <c r="S14" s="226"/>
+      <c r="T14" s="226"/>
+      <c r="U14" s="226"/>
+      <c r="V14" s="226"/>
+      <c r="W14" s="226"/>
+      <c r="X14" s="226"/>
+      <c r="Y14" s="226"/>
+      <c r="Z14" s="226"/>
+      <c r="AA14" s="227"/>
       <c r="AB14" s="130"/>
     </row>
     <row r="15" spans="1:28" s="133" customFormat="1" ht="35.1" customHeight="1">
       <c r="A15" s="131"/>
       <c r="B15" s="132"/>
       <c r="C15" s="129"/>
-      <c r="D15" s="182" t="s">
+      <c r="D15" s="186" t="s">
         <v>243</v>
       </c>
-      <c r="E15" s="183"/>
-      <c r="F15" s="183"/>
-      <c r="G15" s="183"/>
-      <c r="H15" s="184"/>
+      <c r="E15" s="179"/>
+      <c r="F15" s="179"/>
+      <c r="G15" s="179"/>
+      <c r="H15" s="181"/>
       <c r="I15" s="100"/>
-      <c r="J15" s="188" t="s">
+      <c r="J15" s="225" t="s">
         <v>185</v>
       </c>
-      <c r="K15" s="186"/>
-      <c r="L15" s="186"/>
-      <c r="M15" s="186"/>
-      <c r="N15" s="186"/>
-      <c r="O15" s="186"/>
-      <c r="P15" s="186"/>
-      <c r="Q15" s="186"/>
-      <c r="R15" s="186"/>
-      <c r="S15" s="186"/>
-      <c r="T15" s="186"/>
-      <c r="U15" s="186"/>
-      <c r="V15" s="186"/>
-      <c r="W15" s="186"/>
-      <c r="X15" s="186"/>
-      <c r="Y15" s="186"/>
-      <c r="Z15" s="186"/>
-      <c r="AA15" s="187"/>
+      <c r="K15" s="226"/>
+      <c r="L15" s="226"/>
+      <c r="M15" s="226"/>
+      <c r="N15" s="226"/>
+      <c r="O15" s="226"/>
+      <c r="P15" s="226"/>
+      <c r="Q15" s="226"/>
+      <c r="R15" s="226"/>
+      <c r="S15" s="226"/>
+      <c r="T15" s="226"/>
+      <c r="U15" s="226"/>
+      <c r="V15" s="226"/>
+      <c r="W15" s="226"/>
+      <c r="X15" s="226"/>
+      <c r="Y15" s="226"/>
+      <c r="Z15" s="226"/>
+      <c r="AA15" s="227"/>
       <c r="AB15" s="130"/>
     </row>
     <row r="16" spans="1:28" s="133" customFormat="1" ht="35.1" customHeight="1">
       <c r="A16" s="131"/>
       <c r="B16" s="132"/>
       <c r="C16" s="129"/>
-      <c r="D16" s="182" t="s">
+      <c r="D16" s="186" t="s">
         <v>244</v>
       </c>
-      <c r="E16" s="183"/>
-      <c r="F16" s="183"/>
-      <c r="G16" s="183"/>
-      <c r="H16" s="184"/>
+      <c r="E16" s="179"/>
+      <c r="F16" s="179"/>
+      <c r="G16" s="179"/>
+      <c r="H16" s="181"/>
       <c r="I16" s="100"/>
-      <c r="J16" s="188" t="s">
+      <c r="J16" s="225" t="s">
         <v>186</v>
       </c>
-      <c r="K16" s="186"/>
-      <c r="L16" s="186"/>
-      <c r="M16" s="186"/>
-      <c r="N16" s="186"/>
-      <c r="O16" s="186"/>
-      <c r="P16" s="186"/>
-      <c r="Q16" s="186"/>
-      <c r="R16" s="186"/>
-      <c r="S16" s="186"/>
-      <c r="T16" s="186"/>
-      <c r="U16" s="186"/>
-      <c r="V16" s="186"/>
-      <c r="W16" s="186"/>
-      <c r="X16" s="186"/>
-      <c r="Y16" s="186"/>
-      <c r="Z16" s="186"/>
-      <c r="AA16" s="187"/>
+      <c r="K16" s="226"/>
+      <c r="L16" s="226"/>
+      <c r="M16" s="226"/>
+      <c r="N16" s="226"/>
+      <c r="O16" s="226"/>
+      <c r="P16" s="226"/>
+      <c r="Q16" s="226"/>
+      <c r="R16" s="226"/>
+      <c r="S16" s="226"/>
+      <c r="T16" s="226"/>
+      <c r="U16" s="226"/>
+      <c r="V16" s="226"/>
+      <c r="W16" s="226"/>
+      <c r="X16" s="226"/>
+      <c r="Y16" s="226"/>
+      <c r="Z16" s="226"/>
+      <c r="AA16" s="227"/>
       <c r="AB16" s="130"/>
     </row>
     <row r="17" spans="1:28" s="133" customFormat="1" ht="39.950000000000003" customHeight="1">
       <c r="A17" s="131"/>
       <c r="B17" s="132"/>
       <c r="C17" s="129"/>
-      <c r="D17" s="182" t="s">
+      <c r="D17" s="186" t="s">
         <v>245</v>
       </c>
-      <c r="E17" s="183"/>
-      <c r="F17" s="183"/>
-      <c r="G17" s="183"/>
-      <c r="H17" s="184"/>
+      <c r="E17" s="179"/>
+      <c r="F17" s="179"/>
+      <c r="G17" s="179"/>
+      <c r="H17" s="181"/>
       <c r="I17" s="100"/>
-      <c r="J17" s="295" t="s">
+      <c r="J17" s="178" t="s">
         <v>187</v>
       </c>
-      <c r="K17" s="183"/>
-      <c r="L17" s="183"/>
-      <c r="M17" s="183"/>
-      <c r="N17" s="183"/>
-      <c r="O17" s="183"/>
-      <c r="P17" s="183"/>
-      <c r="Q17" s="183"/>
-      <c r="R17" s="296" t="s">
+      <c r="K17" s="179"/>
+      <c r="L17" s="179"/>
+      <c r="M17" s="179"/>
+      <c r="N17" s="179"/>
+      <c r="O17" s="179"/>
+      <c r="P17" s="179"/>
+      <c r="Q17" s="179"/>
+      <c r="R17" s="180" t="s">
         <v>239</v>
       </c>
-      <c r="S17" s="183"/>
-      <c r="T17" s="183"/>
-      <c r="U17" s="183"/>
-      <c r="V17" s="184"/>
-      <c r="W17" s="297" t="s">
+      <c r="S17" s="179"/>
+      <c r="T17" s="179"/>
+      <c r="U17" s="179"/>
+      <c r="V17" s="181"/>
+      <c r="W17" s="182" t="s">
         <v>237</v>
       </c>
-      <c r="X17" s="183"/>
-      <c r="Y17" s="183"/>
+      <c r="X17" s="179"/>
+      <c r="Y17" s="179"/>
       <c r="Z17" s="101" t="s">
         <v>238</v>
       </c>
@@ -10750,72 +10753,72 @@
       <c r="A18" s="116"/>
       <c r="B18" s="128"/>
       <c r="C18" s="134"/>
-      <c r="D18" s="178" t="s">
+      <c r="D18" s="301" t="s">
         <v>246</v>
       </c>
-      <c r="E18" s="179"/>
-      <c r="F18" s="179"/>
-      <c r="G18" s="179"/>
-      <c r="H18" s="180"/>
+      <c r="E18" s="302"/>
+      <c r="F18" s="302"/>
+      <c r="G18" s="302"/>
+      <c r="H18" s="303"/>
       <c r="I18" s="103"/>
-      <c r="J18" s="295" t="s">
+      <c r="J18" s="178" t="s">
         <v>203</v>
       </c>
-      <c r="K18" s="183"/>
-      <c r="L18" s="183"/>
-      <c r="M18" s="183"/>
-      <c r="N18" s="183"/>
-      <c r="O18" s="183"/>
-      <c r="P18" s="183"/>
-      <c r="Q18" s="183"/>
-      <c r="R18" s="296" t="s">
+      <c r="K18" s="179"/>
+      <c r="L18" s="179"/>
+      <c r="M18" s="179"/>
+      <c r="N18" s="179"/>
+      <c r="O18" s="179"/>
+      <c r="P18" s="179"/>
+      <c r="Q18" s="179"/>
+      <c r="R18" s="180" t="s">
         <v>204</v>
       </c>
-      <c r="S18" s="183"/>
-      <c r="T18" s="183"/>
-      <c r="U18" s="183"/>
-      <c r="V18" s="184"/>
-      <c r="W18" s="298" t="s">
+      <c r="S18" s="179"/>
+      <c r="T18" s="179"/>
+      <c r="U18" s="179"/>
+      <c r="V18" s="181"/>
+      <c r="W18" s="183" t="s">
         <v>206</v>
       </c>
-      <c r="X18" s="183"/>
-      <c r="Y18" s="183"/>
-      <c r="Z18" s="183"/>
-      <c r="AA18" s="184"/>
+      <c r="X18" s="179"/>
+      <c r="Y18" s="179"/>
+      <c r="Z18" s="179"/>
+      <c r="AA18" s="181"/>
       <c r="AB18" s="130"/>
     </row>
     <row r="19" spans="1:28" s="106" customFormat="1" ht="35.1" customHeight="1">
       <c r="A19" s="116"/>
       <c r="B19" s="128"/>
       <c r="C19" s="129"/>
-      <c r="D19" s="182" t="s">
+      <c r="D19" s="186" t="s">
         <v>247</v>
       </c>
-      <c r="E19" s="183"/>
-      <c r="F19" s="183"/>
-      <c r="G19" s="183"/>
-      <c r="H19" s="184"/>
+      <c r="E19" s="179"/>
+      <c r="F19" s="179"/>
+      <c r="G19" s="179"/>
+      <c r="H19" s="181"/>
       <c r="I19" s="100"/>
-      <c r="J19" s="286" t="s">
+      <c r="J19" s="221" t="s">
         <v>205</v>
       </c>
-      <c r="K19" s="183"/>
-      <c r="L19" s="183"/>
-      <c r="M19" s="183"/>
-      <c r="N19" s="183"/>
-      <c r="O19" s="183"/>
-      <c r="P19" s="183"/>
-      <c r="Q19" s="183"/>
-      <c r="R19" s="183"/>
-      <c r="S19" s="183"/>
-      <c r="T19" s="183"/>
-      <c r="U19" s="183"/>
-      <c r="V19" s="183"/>
-      <c r="W19" s="183"/>
-      <c r="X19" s="183"/>
-      <c r="Y19" s="183"/>
-      <c r="Z19" s="183"/>
-      <c r="AA19" s="184"/>
+      <c r="K19" s="179"/>
+      <c r="L19" s="179"/>
+      <c r="M19" s="179"/>
+      <c r="N19" s="179"/>
+      <c r="O19" s="179"/>
+      <c r="P19" s="179"/>
+      <c r="Q19" s="179"/>
+      <c r="R19" s="179"/>
+      <c r="S19" s="179"/>
+      <c r="T19" s="179"/>
+      <c r="U19" s="179"/>
+      <c r="V19" s="179"/>
+      <c r="W19" s="179"/>
+      <c r="X19" s="179"/>
+      <c r="Y19" s="179"/>
+      <c r="Z19" s="179"/>
+      <c r="AA19" s="181"/>
       <c r="AB19" s="130"/>
     </row>
     <row r="20" spans="1:28" s="106" customFormat="1" ht="20.100000000000001" customHeight="1">
@@ -10850,46 +10853,46 @@
     <row r="21" spans="1:28" s="139" customFormat="1" ht="35.1" customHeight="1">
       <c r="A21" s="136"/>
       <c r="B21" s="137"/>
-      <c r="C21" s="299" t="s">
+      <c r="C21" s="187" t="s">
         <v>175</v>
       </c>
-      <c r="D21" s="300"/>
-      <c r="E21" s="300"/>
-      <c r="F21" s="300"/>
-      <c r="G21" s="301" t="s">
+      <c r="D21" s="188"/>
+      <c r="E21" s="188"/>
+      <c r="F21" s="188"/>
+      <c r="G21" s="189" t="s">
         <v>248</v>
       </c>
-      <c r="H21" s="301"/>
-      <c r="I21" s="301"/>
-      <c r="J21" s="301"/>
-      <c r="K21" s="302"/>
-      <c r="L21" s="248" t="s">
+      <c r="H21" s="189"/>
+      <c r="I21" s="189"/>
+      <c r="J21" s="189"/>
+      <c r="K21" s="190"/>
+      <c r="L21" s="249" t="s">
         <v>101</v>
       </c>
-      <c r="M21" s="249"/>
-      <c r="N21" s="249"/>
-      <c r="O21" s="250" t="str">
+      <c r="M21" s="250"/>
+      <c r="N21" s="250"/>
+      <c r="O21" s="251" t="str">
         <f>V21</f>
         <v>{합계_금액_부가세}</v>
       </c>
-      <c r="P21" s="236"/>
-      <c r="Q21" s="236"/>
-      <c r="R21" s="236"/>
-      <c r="S21" s="236"/>
+      <c r="P21" s="252"/>
+      <c r="Q21" s="252"/>
+      <c r="R21" s="252"/>
+      <c r="S21" s="252"/>
       <c r="T21" s="111" t="s">
         <v>102</v>
       </c>
       <c r="U21" s="111" t="s">
         <v>103</v>
       </c>
-      <c r="V21" s="251" t="str">
+      <c r="V21" s="253" t="str">
         <f>T27</f>
         <v>{합계_금액_부가세}</v>
       </c>
-      <c r="W21" s="251"/>
-      <c r="X21" s="251"/>
-      <c r="Y21" s="251"/>
-      <c r="Z21" s="251"/>
+      <c r="W21" s="253"/>
+      <c r="X21" s="253"/>
+      <c r="Y21" s="253"/>
+      <c r="Z21" s="253"/>
       <c r="AA21" s="112" t="s">
         <v>120</v>
       </c>
@@ -10898,194 +10901,194 @@
     <row r="22" spans="1:28" s="106" customFormat="1" ht="35.1" customHeight="1">
       <c r="A22" s="116"/>
       <c r="B22" s="140"/>
-      <c r="C22" s="253" t="s">
+      <c r="C22" s="222" t="s">
         <v>121</v>
       </c>
-      <c r="D22" s="254"/>
-      <c r="E22" s="252" t="s">
+      <c r="D22" s="223"/>
+      <c r="E22" s="224" t="s">
         <v>104</v>
       </c>
-      <c r="F22" s="253"/>
-      <c r="G22" s="253"/>
-      <c r="H22" s="253"/>
-      <c r="I22" s="253"/>
-      <c r="J22" s="253"/>
-      <c r="K22" s="254"/>
-      <c r="L22" s="252" t="s">
+      <c r="F22" s="222"/>
+      <c r="G22" s="222"/>
+      <c r="H22" s="222"/>
+      <c r="I22" s="222"/>
+      <c r="J22" s="222"/>
+      <c r="K22" s="223"/>
+      <c r="L22" s="224" t="s">
         <v>122</v>
       </c>
-      <c r="M22" s="253"/>
-      <c r="N22" s="253"/>
-      <c r="O22" s="253"/>
-      <c r="P22" s="252" t="s">
+      <c r="M22" s="222"/>
+      <c r="N22" s="222"/>
+      <c r="O22" s="222"/>
+      <c r="P22" s="224" t="s">
         <v>123</v>
       </c>
-      <c r="Q22" s="253"/>
-      <c r="R22" s="253"/>
-      <c r="S22" s="254"/>
-      <c r="T22" s="252" t="s">
+      <c r="Q22" s="222"/>
+      <c r="R22" s="222"/>
+      <c r="S22" s="223"/>
+      <c r="T22" s="224" t="s">
         <v>105</v>
       </c>
-      <c r="U22" s="253"/>
-      <c r="V22" s="253"/>
-      <c r="W22" s="253"/>
-      <c r="X22" s="254"/>
-      <c r="Y22" s="253" t="s">
+      <c r="U22" s="222"/>
+      <c r="V22" s="222"/>
+      <c r="W22" s="222"/>
+      <c r="X22" s="223"/>
+      <c r="Y22" s="222" t="s">
         <v>138</v>
       </c>
-      <c r="Z22" s="253"/>
-      <c r="AA22" s="254"/>
+      <c r="Z22" s="222"/>
+      <c r="AA22" s="223"/>
       <c r="AB22" s="114"/>
     </row>
     <row r="23" spans="1:28" s="106" customFormat="1" ht="35.1" customHeight="1">
       <c r="A23" s="116"/>
       <c r="B23" s="140"/>
-      <c r="C23" s="246">
+      <c r="C23" s="207">
         <v>1</v>
       </c>
-      <c r="D23" s="247"/>
-      <c r="E23" s="245" t="s">
+      <c r="D23" s="208"/>
+      <c r="E23" s="209" t="s">
         <v>126</v>
       </c>
-      <c r="F23" s="246"/>
-      <c r="G23" s="246"/>
-      <c r="H23" s="246"/>
-      <c r="I23" s="246"/>
-      <c r="J23" s="246"/>
-      <c r="K23" s="247"/>
-      <c r="L23" s="245" t="s">
+      <c r="F23" s="207"/>
+      <c r="G23" s="207"/>
+      <c r="H23" s="207"/>
+      <c r="I23" s="207"/>
+      <c r="J23" s="207"/>
+      <c r="K23" s="208"/>
+      <c r="L23" s="209" t="s">
         <v>124</v>
       </c>
-      <c r="M23" s="246"/>
-      <c r="N23" s="246"/>
-      <c r="O23" s="247"/>
-      <c r="P23" s="216" t="s">
+      <c r="M23" s="207"/>
+      <c r="N23" s="207"/>
+      <c r="O23" s="208"/>
+      <c r="P23" s="254" t="s">
         <v>188</v>
       </c>
-      <c r="Q23" s="217"/>
-      <c r="R23" s="217"/>
-      <c r="S23" s="218"/>
-      <c r="T23" s="219" t="s">
+      <c r="Q23" s="255"/>
+      <c r="R23" s="255"/>
+      <c r="S23" s="256"/>
+      <c r="T23" s="191" t="s">
         <v>191</v>
       </c>
-      <c r="U23" s="220"/>
-      <c r="V23" s="220"/>
-      <c r="W23" s="220"/>
-      <c r="X23" s="221"/>
-      <c r="Y23" s="303"/>
-      <c r="Z23" s="303"/>
-      <c r="AA23" s="304"/>
+      <c r="U23" s="192"/>
+      <c r="V23" s="192"/>
+      <c r="W23" s="192"/>
+      <c r="X23" s="193"/>
+      <c r="Y23" s="194"/>
+      <c r="Z23" s="194"/>
+      <c r="AA23" s="195"/>
       <c r="AB23" s="114"/>
     </row>
     <row r="24" spans="1:28" s="106" customFormat="1" ht="35.1" customHeight="1">
       <c r="A24" s="116"/>
       <c r="B24" s="140"/>
-      <c r="C24" s="201">
+      <c r="C24" s="258">
         <v>2</v>
       </c>
-      <c r="D24" s="202"/>
-      <c r="E24" s="203" t="s">
+      <c r="D24" s="259"/>
+      <c r="E24" s="257" t="s">
         <v>176</v>
       </c>
-      <c r="F24" s="201"/>
-      <c r="G24" s="201"/>
-      <c r="H24" s="201"/>
-      <c r="I24" s="201"/>
-      <c r="J24" s="201"/>
-      <c r="K24" s="202"/>
-      <c r="L24" s="203" t="s">
+      <c r="F24" s="258"/>
+      <c r="G24" s="258"/>
+      <c r="H24" s="258"/>
+      <c r="I24" s="258"/>
+      <c r="J24" s="258"/>
+      <c r="K24" s="259"/>
+      <c r="L24" s="257" t="s">
         <v>177</v>
       </c>
-      <c r="M24" s="201"/>
-      <c r="N24" s="201"/>
-      <c r="O24" s="202"/>
-      <c r="P24" s="216" t="s">
+      <c r="M24" s="258"/>
+      <c r="N24" s="258"/>
+      <c r="O24" s="259"/>
+      <c r="P24" s="254" t="s">
         <v>189</v>
       </c>
-      <c r="Q24" s="217"/>
-      <c r="R24" s="217"/>
-      <c r="S24" s="218"/>
-      <c r="T24" s="219" t="s">
+      <c r="Q24" s="255"/>
+      <c r="R24" s="255"/>
+      <c r="S24" s="256"/>
+      <c r="T24" s="191" t="s">
         <v>192</v>
       </c>
-      <c r="U24" s="220"/>
-      <c r="V24" s="220"/>
-      <c r="W24" s="220"/>
-      <c r="X24" s="221"/>
-      <c r="Y24" s="222"/>
-      <c r="Z24" s="222"/>
-      <c r="AA24" s="223"/>
+      <c r="U24" s="192"/>
+      <c r="V24" s="192"/>
+      <c r="W24" s="192"/>
+      <c r="X24" s="193"/>
+      <c r="Y24" s="260"/>
+      <c r="Z24" s="260"/>
+      <c r="AA24" s="261"/>
       <c r="AB24" s="114"/>
     </row>
     <row r="25" spans="1:28" s="106" customFormat="1" ht="35.1" customHeight="1">
       <c r="A25" s="116"/>
       <c r="B25" s="140"/>
-      <c r="C25" s="201">
+      <c r="C25" s="258">
         <v>3</v>
       </c>
-      <c r="D25" s="202"/>
-      <c r="E25" s="203" t="s">
+      <c r="D25" s="259"/>
+      <c r="E25" s="257" t="s">
         <v>178</v>
       </c>
-      <c r="F25" s="201"/>
-      <c r="G25" s="201"/>
-      <c r="H25" s="201"/>
-      <c r="I25" s="201"/>
-      <c r="J25" s="201"/>
-      <c r="K25" s="202"/>
-      <c r="L25" s="203" t="s">
+      <c r="F25" s="258"/>
+      <c r="G25" s="258"/>
+      <c r="H25" s="258"/>
+      <c r="I25" s="258"/>
+      <c r="J25" s="258"/>
+      <c r="K25" s="259"/>
+      <c r="L25" s="257" t="s">
         <v>179</v>
       </c>
-      <c r="M25" s="201"/>
-      <c r="N25" s="201"/>
-      <c r="O25" s="202"/>
-      <c r="P25" s="216" t="s">
+      <c r="M25" s="258"/>
+      <c r="N25" s="258"/>
+      <c r="O25" s="259"/>
+      <c r="P25" s="254" t="s">
         <v>190</v>
       </c>
-      <c r="Q25" s="217"/>
-      <c r="R25" s="217"/>
-      <c r="S25" s="218"/>
-      <c r="T25" s="241" t="s">
+      <c r="Q25" s="255"/>
+      <c r="R25" s="255"/>
+      <c r="S25" s="256"/>
+      <c r="T25" s="281" t="s">
         <v>193</v>
       </c>
-      <c r="U25" s="242"/>
-      <c r="V25" s="242"/>
-      <c r="W25" s="242"/>
-      <c r="X25" s="243"/>
-      <c r="Y25" s="211"/>
-      <c r="Z25" s="211"/>
-      <c r="AA25" s="212"/>
+      <c r="U25" s="282"/>
+      <c r="V25" s="282"/>
+      <c r="W25" s="282"/>
+      <c r="X25" s="283"/>
+      <c r="Y25" s="292"/>
+      <c r="Z25" s="292"/>
+      <c r="AA25" s="293"/>
       <c r="AB25" s="114"/>
     </row>
     <row r="26" spans="1:28" s="144" customFormat="1" ht="35.1" customHeight="1">
       <c r="A26" s="141"/>
       <c r="B26" s="142"/>
-      <c r="C26" s="233" t="s">
+      <c r="C26" s="274" t="s">
         <v>125</v>
       </c>
-      <c r="D26" s="234"/>
-      <c r="E26" s="234"/>
-      <c r="F26" s="234"/>
-      <c r="G26" s="234"/>
-      <c r="H26" s="234"/>
-      <c r="I26" s="234"/>
-      <c r="J26" s="234"/>
-      <c r="K26" s="244"/>
-      <c r="L26" s="233"/>
-      <c r="M26" s="234"/>
-      <c r="N26" s="234"/>
-      <c r="O26" s="234"/>
-      <c r="P26" s="235"/>
-      <c r="Q26" s="236"/>
-      <c r="R26" s="236"/>
-      <c r="S26" s="237"/>
-      <c r="T26" s="238" t="s">
+      <c r="D26" s="275"/>
+      <c r="E26" s="275"/>
+      <c r="F26" s="275"/>
+      <c r="G26" s="275"/>
+      <c r="H26" s="275"/>
+      <c r="I26" s="275"/>
+      <c r="J26" s="275"/>
+      <c r="K26" s="284"/>
+      <c r="L26" s="274"/>
+      <c r="M26" s="275"/>
+      <c r="N26" s="275"/>
+      <c r="O26" s="275"/>
+      <c r="P26" s="276"/>
+      <c r="Q26" s="252"/>
+      <c r="R26" s="252"/>
+      <c r="S26" s="277"/>
+      <c r="T26" s="278" t="s">
         <v>194</v>
       </c>
-      <c r="U26" s="239"/>
-      <c r="V26" s="239"/>
-      <c r="W26" s="239"/>
-      <c r="X26" s="240"/>
+      <c r="U26" s="279"/>
+      <c r="V26" s="279"/>
+      <c r="W26" s="279"/>
+      <c r="X26" s="280"/>
       <c r="Y26" s="109"/>
       <c r="Z26" s="109"/>
       <c r="AA26" s="110"/>
@@ -11094,132 +11097,132 @@
     <row r="27" spans="1:28" s="144" customFormat="1" ht="35.1" customHeight="1">
       <c r="A27" s="141"/>
       <c r="B27" s="142"/>
-      <c r="C27" s="224" t="s">
+      <c r="C27" s="262" t="s">
         <v>180</v>
       </c>
-      <c r="D27" s="225"/>
-      <c r="E27" s="225"/>
-      <c r="F27" s="225"/>
-      <c r="G27" s="225"/>
-      <c r="H27" s="225"/>
-      <c r="I27" s="225"/>
-      <c r="J27" s="225"/>
-      <c r="K27" s="225"/>
-      <c r="L27" s="225"/>
-      <c r="M27" s="225"/>
-      <c r="N27" s="225"/>
-      <c r="O27" s="225"/>
-      <c r="P27" s="225"/>
-      <c r="Q27" s="225"/>
-      <c r="R27" s="225"/>
-      <c r="S27" s="226"/>
-      <c r="T27" s="213" t="s">
+      <c r="D27" s="263"/>
+      <c r="E27" s="263"/>
+      <c r="F27" s="263"/>
+      <c r="G27" s="263"/>
+      <c r="H27" s="263"/>
+      <c r="I27" s="263"/>
+      <c r="J27" s="263"/>
+      <c r="K27" s="263"/>
+      <c r="L27" s="263"/>
+      <c r="M27" s="263"/>
+      <c r="N27" s="263"/>
+      <c r="O27" s="263"/>
+      <c r="P27" s="263"/>
+      <c r="Q27" s="263"/>
+      <c r="R27" s="263"/>
+      <c r="S27" s="264"/>
+      <c r="T27" s="265" t="s">
         <v>195</v>
       </c>
-      <c r="U27" s="214"/>
-      <c r="V27" s="214"/>
-      <c r="W27" s="214"/>
-      <c r="X27" s="215"/>
-      <c r="Y27" s="227" t="s">
+      <c r="U27" s="266"/>
+      <c r="V27" s="266"/>
+      <c r="W27" s="266"/>
+      <c r="X27" s="267"/>
+      <c r="Y27" s="268" t="s">
         <v>182</v>
       </c>
-      <c r="Z27" s="228"/>
-      <c r="AA27" s="229"/>
+      <c r="Z27" s="269"/>
+      <c r="AA27" s="270"/>
       <c r="AB27" s="143"/>
     </row>
     <row r="28" spans="1:28" s="144" customFormat="1" ht="35.1" customHeight="1">
       <c r="A28" s="141"/>
       <c r="B28" s="142"/>
-      <c r="C28" s="224" t="s">
+      <c r="C28" s="262" t="s">
         <v>181</v>
       </c>
-      <c r="D28" s="225"/>
-      <c r="E28" s="225"/>
-      <c r="F28" s="225"/>
-      <c r="G28" s="225"/>
-      <c r="H28" s="225"/>
-      <c r="I28" s="225"/>
-      <c r="J28" s="225"/>
-      <c r="K28" s="225"/>
-      <c r="L28" s="225"/>
-      <c r="M28" s="225"/>
-      <c r="N28" s="225"/>
-      <c r="O28" s="225"/>
-      <c r="P28" s="225"/>
-      <c r="Q28" s="225"/>
-      <c r="R28" s="225"/>
-      <c r="S28" s="226"/>
-      <c r="T28" s="213" t="s">
+      <c r="D28" s="263"/>
+      <c r="E28" s="263"/>
+      <c r="F28" s="263"/>
+      <c r="G28" s="263"/>
+      <c r="H28" s="263"/>
+      <c r="I28" s="263"/>
+      <c r="J28" s="263"/>
+      <c r="K28" s="263"/>
+      <c r="L28" s="263"/>
+      <c r="M28" s="263"/>
+      <c r="N28" s="263"/>
+      <c r="O28" s="263"/>
+      <c r="P28" s="263"/>
+      <c r="Q28" s="263"/>
+      <c r="R28" s="263"/>
+      <c r="S28" s="264"/>
+      <c r="T28" s="265" t="s">
         <v>196</v>
       </c>
-      <c r="U28" s="214"/>
-      <c r="V28" s="214"/>
-      <c r="W28" s="214"/>
-      <c r="X28" s="215"/>
-      <c r="Y28" s="230"/>
-      <c r="Z28" s="231"/>
-      <c r="AA28" s="232"/>
+      <c r="U28" s="266"/>
+      <c r="V28" s="266"/>
+      <c r="W28" s="266"/>
+      <c r="X28" s="267"/>
+      <c r="Y28" s="271"/>
+      <c r="Z28" s="272"/>
+      <c r="AA28" s="273"/>
       <c r="AB28" s="143"/>
     </row>
     <row r="29" spans="1:28" s="106" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="A29" s="116"/>
-      <c r="C29" s="207"/>
-      <c r="D29" s="207"/>
-      <c r="E29" s="207"/>
-      <c r="F29" s="207"/>
-      <c r="G29" s="207"/>
-      <c r="H29" s="207"/>
-      <c r="I29" s="207"/>
-      <c r="J29" s="207"/>
-      <c r="K29" s="207"/>
-      <c r="L29" s="208"/>
-      <c r="M29" s="208"/>
-      <c r="N29" s="208"/>
-      <c r="O29" s="208"/>
-      <c r="P29" s="208"/>
-      <c r="Q29" s="208"/>
-      <c r="R29" s="208"/>
-      <c r="S29" s="208"/>
-      <c r="T29" s="209"/>
-      <c r="U29" s="209"/>
-      <c r="V29" s="209"/>
-      <c r="W29" s="209"/>
-      <c r="X29" s="209"/>
-      <c r="Y29" s="210"/>
-      <c r="Z29" s="210"/>
-      <c r="AA29" s="210"/>
+      <c r="C29" s="288"/>
+      <c r="D29" s="288"/>
+      <c r="E29" s="288"/>
+      <c r="F29" s="288"/>
+      <c r="G29" s="288"/>
+      <c r="H29" s="288"/>
+      <c r="I29" s="288"/>
+      <c r="J29" s="288"/>
+      <c r="K29" s="288"/>
+      <c r="L29" s="289"/>
+      <c r="M29" s="289"/>
+      <c r="N29" s="289"/>
+      <c r="O29" s="289"/>
+      <c r="P29" s="289"/>
+      <c r="Q29" s="289"/>
+      <c r="R29" s="289"/>
+      <c r="S29" s="289"/>
+      <c r="T29" s="290"/>
+      <c r="U29" s="290"/>
+      <c r="V29" s="290"/>
+      <c r="W29" s="290"/>
+      <c r="X29" s="290"/>
+      <c r="Y29" s="291"/>
+      <c r="Z29" s="291"/>
+      <c r="AA29" s="291"/>
       <c r="AB29" s="114"/>
     </row>
     <row r="30" spans="1:28" s="106" customFormat="1" ht="35.1" customHeight="1">
       <c r="A30" s="116"/>
       <c r="B30" s="128"/>
-      <c r="C30" s="204" t="s">
+      <c r="C30" s="285" t="s">
         <v>157</v>
       </c>
-      <c r="D30" s="205"/>
-      <c r="E30" s="205"/>
-      <c r="F30" s="205"/>
-      <c r="G30" s="205"/>
-      <c r="H30" s="205"/>
-      <c r="I30" s="205"/>
-      <c r="J30" s="205"/>
-      <c r="K30" s="205"/>
-      <c r="L30" s="205"/>
-      <c r="M30" s="205"/>
-      <c r="N30" s="205"/>
-      <c r="O30" s="205"/>
-      <c r="P30" s="205"/>
-      <c r="Q30" s="205"/>
-      <c r="R30" s="205"/>
-      <c r="S30" s="205"/>
-      <c r="T30" s="205"/>
-      <c r="U30" s="205"/>
-      <c r="V30" s="205"/>
-      <c r="W30" s="205"/>
-      <c r="X30" s="205"/>
-      <c r="Y30" s="205"/>
-      <c r="Z30" s="205"/>
-      <c r="AA30" s="206"/>
+      <c r="D30" s="286"/>
+      <c r="E30" s="286"/>
+      <c r="F30" s="286"/>
+      <c r="G30" s="286"/>
+      <c r="H30" s="286"/>
+      <c r="I30" s="286"/>
+      <c r="J30" s="286"/>
+      <c r="K30" s="286"/>
+      <c r="L30" s="286"/>
+      <c r="M30" s="286"/>
+      <c r="N30" s="286"/>
+      <c r="O30" s="286"/>
+      <c r="P30" s="286"/>
+      <c r="Q30" s="286"/>
+      <c r="R30" s="286"/>
+      <c r="S30" s="286"/>
+      <c r="T30" s="286"/>
+      <c r="U30" s="286"/>
+      <c r="V30" s="286"/>
+      <c r="W30" s="286"/>
+      <c r="X30" s="286"/>
+      <c r="Y30" s="286"/>
+      <c r="Z30" s="286"/>
+      <c r="AA30" s="287"/>
       <c r="AB30" s="114"/>
     </row>
     <row r="31" spans="1:28" s="152" customFormat="1" ht="35.1" hidden="1" customHeight="1">
@@ -11257,33 +11260,33 @@
     <row r="32" spans="1:28" s="160" customFormat="1" ht="35.1" customHeight="1">
       <c r="A32" s="153"/>
       <c r="B32" s="154"/>
-      <c r="C32" s="292" t="s">
+      <c r="C32" s="172" t="s">
         <v>249</v>
       </c>
-      <c r="D32" s="293"/>
-      <c r="E32" s="293"/>
-      <c r="F32" s="293"/>
-      <c r="G32" s="293"/>
-      <c r="H32" s="293"/>
-      <c r="I32" s="293"/>
-      <c r="J32" s="293"/>
-      <c r="K32" s="293"/>
-      <c r="L32" s="293"/>
-      <c r="M32" s="293"/>
-      <c r="N32" s="293"/>
-      <c r="O32" s="293"/>
-      <c r="P32" s="293"/>
-      <c r="Q32" s="293"/>
-      <c r="R32" s="293"/>
-      <c r="S32" s="293"/>
-      <c r="T32" s="293"/>
-      <c r="U32" s="293"/>
-      <c r="V32" s="293"/>
-      <c r="W32" s="293"/>
-      <c r="X32" s="293"/>
-      <c r="Y32" s="293"/>
-      <c r="Z32" s="293"/>
-      <c r="AA32" s="294"/>
+      <c r="D32" s="173"/>
+      <c r="E32" s="173"/>
+      <c r="F32" s="173"/>
+      <c r="G32" s="173"/>
+      <c r="H32" s="173"/>
+      <c r="I32" s="173"/>
+      <c r="J32" s="173"/>
+      <c r="K32" s="173"/>
+      <c r="L32" s="173"/>
+      <c r="M32" s="173"/>
+      <c r="N32" s="173"/>
+      <c r="O32" s="173"/>
+      <c r="P32" s="173"/>
+      <c r="Q32" s="173"/>
+      <c r="R32" s="173"/>
+      <c r="S32" s="173"/>
+      <c r="T32" s="173"/>
+      <c r="U32" s="173"/>
+      <c r="V32" s="173"/>
+      <c r="W32" s="173"/>
+      <c r="X32" s="173"/>
+      <c r="Y32" s="173"/>
+      <c r="Z32" s="173"/>
+      <c r="AA32" s="174"/>
       <c r="AB32" s="159"/>
     </row>
     <row r="33" spans="1:28" s="160" customFormat="1" ht="35.1" customHeight="1">
@@ -11442,6 +11445,84 @@
     </row>
   </sheetData>
   <mergeCells count="94">
+    <mergeCell ref="X10:AA10"/>
+    <mergeCell ref="T28:X28"/>
+    <mergeCell ref="A1:AB1"/>
+    <mergeCell ref="A4:AA4"/>
+    <mergeCell ref="E7:J7"/>
+    <mergeCell ref="D18:H18"/>
+    <mergeCell ref="F13:J13"/>
+    <mergeCell ref="F12:J12"/>
+    <mergeCell ref="D14:H14"/>
+    <mergeCell ref="J14:AA14"/>
+    <mergeCell ref="D16:H16"/>
+    <mergeCell ref="J16:AA16"/>
+    <mergeCell ref="D17:H17"/>
+    <mergeCell ref="D15:H15"/>
+    <mergeCell ref="N9:P9"/>
+    <mergeCell ref="Q9:AA9"/>
+    <mergeCell ref="N10:P10"/>
+    <mergeCell ref="C30:AA30"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="E29:K29"/>
+    <mergeCell ref="L29:O29"/>
+    <mergeCell ref="P29:S29"/>
+    <mergeCell ref="T29:X29"/>
+    <mergeCell ref="Y29:AA29"/>
+    <mergeCell ref="T24:X24"/>
+    <mergeCell ref="Y24:AA24"/>
+    <mergeCell ref="C28:S28"/>
+    <mergeCell ref="C27:S27"/>
+    <mergeCell ref="T27:X27"/>
+    <mergeCell ref="Y27:AA28"/>
+    <mergeCell ref="L26:O26"/>
+    <mergeCell ref="P26:S26"/>
+    <mergeCell ref="T26:X26"/>
+    <mergeCell ref="T25:X25"/>
+    <mergeCell ref="C26:K26"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="E24:K24"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="E25:K25"/>
+    <mergeCell ref="Y25:AA25"/>
+    <mergeCell ref="L23:O23"/>
+    <mergeCell ref="P23:S23"/>
+    <mergeCell ref="L24:O24"/>
+    <mergeCell ref="L25:O25"/>
+    <mergeCell ref="P25:S25"/>
+    <mergeCell ref="P24:S24"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="O21:S21"/>
+    <mergeCell ref="V21:Z21"/>
+    <mergeCell ref="T22:X22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:K22"/>
+    <mergeCell ref="L22:O22"/>
+    <mergeCell ref="Q8:T8"/>
+    <mergeCell ref="A2:AA2"/>
+    <mergeCell ref="W6:AA6"/>
+    <mergeCell ref="N7:P7"/>
+    <mergeCell ref="Q7:AA7"/>
+    <mergeCell ref="M5:S6"/>
+    <mergeCell ref="U8:W8"/>
+    <mergeCell ref="X8:AA8"/>
+    <mergeCell ref="A3:AB3"/>
+    <mergeCell ref="U10:W10"/>
+    <mergeCell ref="Q10:T10"/>
+    <mergeCell ref="M7:M12"/>
+    <mergeCell ref="N8:P8"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:K23"/>
+    <mergeCell ref="N11:P12"/>
+    <mergeCell ref="Q11:T12"/>
+    <mergeCell ref="U11:W11"/>
+    <mergeCell ref="J19:AA19"/>
+    <mergeCell ref="Y22:AA22"/>
+    <mergeCell ref="P22:S22"/>
+    <mergeCell ref="J15:AA15"/>
+    <mergeCell ref="N13:P13"/>
+    <mergeCell ref="Q13:T13"/>
+    <mergeCell ref="U12:W12"/>
     <mergeCell ref="C32:AA32"/>
     <mergeCell ref="X11:AA11"/>
     <mergeCell ref="J17:Q17"/>
@@ -11458,89 +11539,11 @@
     <mergeCell ref="G21:K21"/>
     <mergeCell ref="T23:X23"/>
     <mergeCell ref="Y23:AA23"/>
-    <mergeCell ref="U10:W10"/>
-    <mergeCell ref="Q10:T10"/>
-    <mergeCell ref="M7:M12"/>
-    <mergeCell ref="N8:P8"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:K23"/>
-    <mergeCell ref="N11:P12"/>
-    <mergeCell ref="Q11:T12"/>
-    <mergeCell ref="U11:W11"/>
-    <mergeCell ref="J19:AA19"/>
-    <mergeCell ref="Y22:AA22"/>
-    <mergeCell ref="P22:S22"/>
-    <mergeCell ref="J15:AA15"/>
-    <mergeCell ref="N13:P13"/>
-    <mergeCell ref="Q13:T13"/>
-    <mergeCell ref="U12:W12"/>
-    <mergeCell ref="Q8:T8"/>
-    <mergeCell ref="A2:AA2"/>
-    <mergeCell ref="W6:AA6"/>
-    <mergeCell ref="N7:P7"/>
-    <mergeCell ref="Q7:AA7"/>
-    <mergeCell ref="M5:S6"/>
-    <mergeCell ref="U8:W8"/>
-    <mergeCell ref="X8:AA8"/>
-    <mergeCell ref="A3:AB3"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="O21:S21"/>
-    <mergeCell ref="V21:Z21"/>
-    <mergeCell ref="T22:X22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:K22"/>
-    <mergeCell ref="L22:O22"/>
-    <mergeCell ref="L23:O23"/>
-    <mergeCell ref="P23:S23"/>
-    <mergeCell ref="L24:O24"/>
-    <mergeCell ref="L25:O25"/>
-    <mergeCell ref="P25:S25"/>
-    <mergeCell ref="P24:S24"/>
-    <mergeCell ref="T24:X24"/>
-    <mergeCell ref="Y24:AA24"/>
-    <mergeCell ref="C28:S28"/>
-    <mergeCell ref="C27:S27"/>
-    <mergeCell ref="T27:X27"/>
-    <mergeCell ref="Y27:AA28"/>
-    <mergeCell ref="L26:O26"/>
-    <mergeCell ref="P26:S26"/>
-    <mergeCell ref="T26:X26"/>
-    <mergeCell ref="T25:X25"/>
-    <mergeCell ref="C26:K26"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="E24:K24"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="E25:K25"/>
-    <mergeCell ref="C30:AA30"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="E29:K29"/>
-    <mergeCell ref="L29:O29"/>
-    <mergeCell ref="P29:S29"/>
-    <mergeCell ref="T29:X29"/>
-    <mergeCell ref="Y29:AA29"/>
-    <mergeCell ref="Y25:AA25"/>
-    <mergeCell ref="T28:X28"/>
-    <mergeCell ref="A1:AB1"/>
-    <mergeCell ref="A4:AA4"/>
-    <mergeCell ref="E7:J7"/>
-    <mergeCell ref="D18:H18"/>
-    <mergeCell ref="F13:J13"/>
-    <mergeCell ref="F12:J12"/>
-    <mergeCell ref="D14:H14"/>
-    <mergeCell ref="J14:AA14"/>
-    <mergeCell ref="D16:H16"/>
-    <mergeCell ref="J16:AA16"/>
-    <mergeCell ref="D17:H17"/>
-    <mergeCell ref="D15:H15"/>
-    <mergeCell ref="N9:P9"/>
-    <mergeCell ref="Q9:AA9"/>
-    <mergeCell ref="N10:P10"/>
-    <mergeCell ref="X10:AA10"/>
   </mergeCells>
   <phoneticPr fontId="95" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.84" bottom="0.34" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="9" scale="61" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="64" fitToHeight="0" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>
@@ -11549,6 +11552,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet6">
     <tabColor rgb="FF00B0F0"/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:L48"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
@@ -11566,15 +11570,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="35.25" customHeight="1">
-      <c r="A1" s="307" t="s">
+      <c r="A1" s="308" t="s">
         <v>89</v>
       </c>
-      <c r="B1" s="307"/>
-      <c r="C1" s="307"/>
-      <c r="D1" s="307"/>
-      <c r="E1" s="307"/>
-      <c r="F1" s="307"/>
-      <c r="G1" s="307"/>
+      <c r="B1" s="308"/>
+      <c r="C1" s="308"/>
+      <c r="D1" s="308"/>
+      <c r="E1" s="308"/>
+      <c r="F1" s="308"/>
+      <c r="G1" s="308"/>
     </row>
     <row r="2" spans="1:12" ht="50.1" customHeight="1" thickBot="1">
       <c r="A2" s="12"/>
@@ -11585,10 +11589,10 @@
       <c r="F2" s="12"/>
     </row>
     <row r="3" spans="1:12" ht="30" customHeight="1" thickBot="1">
-      <c r="A3" s="305" t="s">
+      <c r="A3" s="306" t="s">
         <v>150</v>
       </c>
-      <c r="B3" s="306"/>
+      <c r="B3" s="307"/>
       <c r="C3" s="13"/>
       <c r="D3" s="13"/>
       <c r="E3" s="13"/>
@@ -11641,10 +11645,10 @@
       <c r="G5" s="26"/>
     </row>
     <row r="6" spans="1:12" ht="27.95" customHeight="1">
-      <c r="A6" s="312" t="s">
+      <c r="A6" s="313" t="s">
         <v>2</v>
       </c>
-      <c r="B6" s="313"/>
+      <c r="B6" s="314"/>
       <c r="C6" s="98" t="s">
         <v>144</v>
       </c>
@@ -11661,10 +11665,10 @@
       <c r="G6" s="28"/>
     </row>
     <row r="7" spans="1:12" ht="27.95" customHeight="1">
-      <c r="A7" s="312" t="s">
+      <c r="A7" s="313" t="s">
         <v>16</v>
       </c>
-      <c r="B7" s="313"/>
+      <c r="B7" s="314"/>
       <c r="C7" s="98" t="s">
         <v>145</v>
       </c>
@@ -11681,10 +11685,10 @@
       <c r="G7" s="28"/>
     </row>
     <row r="8" spans="1:12" ht="27.95" customHeight="1">
-      <c r="A8" s="312" t="s">
+      <c r="A8" s="313" t="s">
         <v>17</v>
       </c>
-      <c r="B8" s="313"/>
+      <c r="B8" s="314"/>
       <c r="C8" s="98" t="s">
         <v>145</v>
       </c>
@@ -11827,10 +11831,10 @@
       <c r="F15" s="12"/>
     </row>
     <row r="16" spans="1:12" ht="30" customHeight="1" thickBot="1">
-      <c r="A16" s="308" t="s">
+      <c r="A16" s="309" t="s">
         <v>168</v>
       </c>
-      <c r="B16" s="309"/>
+      <c r="B16" s="310"/>
       <c r="C16" s="13"/>
       <c r="D16" s="13"/>
       <c r="E16" s="13"/>
@@ -11876,10 +11880,10 @@
       <c r="G18" s="26"/>
     </row>
     <row r="19" spans="1:7" ht="27.95" customHeight="1">
-      <c r="A19" s="310" t="s">
+      <c r="A19" s="311" t="s">
         <v>16</v>
       </c>
-      <c r="B19" s="311"/>
+      <c r="B19" s="312"/>
       <c r="C19" s="97" t="s">
         <v>167</v>
       </c>
@@ -11896,10 +11900,10 @@
       <c r="G19" s="28"/>
     </row>
     <row r="20" spans="1:7" ht="27.95" customHeight="1">
-      <c r="A20" s="310" t="s">
+      <c r="A20" s="311" t="s">
         <v>132</v>
       </c>
-      <c r="B20" s="311"/>
+      <c r="B20" s="312"/>
       <c r="C20" s="97" t="s">
         <v>167</v>
       </c>
@@ -12055,7 +12059,7 @@
   <phoneticPr fontId="2" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.31496062992125984" right="0.31496062992125984" top="0.86614173228346458" bottom="0.55118110236220474" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="9" scale="85" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="94" fitToHeight="0" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>
@@ -12064,6 +12068,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr codeName="Sheet8">
     <tabColor rgb="FF00FF00"/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E34"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
@@ -12077,19 +12082,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="60" customHeight="1" thickBot="1">
-      <c r="A1" s="321" t="s">
+      <c r="A1" s="315" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="321"/>
-      <c r="C1" s="321"/>
-      <c r="D1" s="321"/>
-      <c r="E1" s="321"/>
+      <c r="B1" s="315"/>
+      <c r="C1" s="315"/>
+      <c r="D1" s="315"/>
+      <c r="E1" s="315"/>
     </row>
     <row r="2" spans="1:5" ht="38.25" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A2" s="316" t="s">
+      <c r="A2" s="319" t="s">
         <v>48</v>
       </c>
-      <c r="B2" s="317"/>
+      <c r="B2" s="320"/>
       <c r="C2" s="82" t="s">
         <v>97</v>
       </c>
@@ -12101,7 +12106,7 @@
       </c>
     </row>
     <row r="3" spans="1:5" ht="24.95" customHeight="1" thickTop="1">
-      <c r="A3" s="322" t="s">
+      <c r="A3" s="316" t="s">
         <v>37</v>
       </c>
       <c r="B3" s="78" t="s">
@@ -12119,7 +12124,7 @@
       </c>
     </row>
     <row r="4" spans="1:5" ht="24.95" customHeight="1">
-      <c r="A4" s="314"/>
+      <c r="A4" s="317"/>
       <c r="B4" s="65" t="s">
         <v>22</v>
       </c>
@@ -12135,7 +12140,7 @@
       </c>
     </row>
     <row r="5" spans="1:5" ht="24.95" customHeight="1">
-      <c r="A5" s="314"/>
+      <c r="A5" s="317"/>
       <c r="B5" s="65" t="s">
         <v>241</v>
       </c>
@@ -12151,7 +12156,7 @@
       </c>
     </row>
     <row r="6" spans="1:5" ht="24.95" customHeight="1">
-      <c r="A6" s="314"/>
+      <c r="A6" s="317"/>
       <c r="B6" s="65" t="s">
         <v>23</v>
       </c>
@@ -12167,7 +12172,7 @@
       </c>
     </row>
     <row r="7" spans="1:5" ht="24.95" customHeight="1">
-      <c r="A7" s="314"/>
+      <c r="A7" s="317"/>
       <c r="B7" s="65" t="s">
         <v>24</v>
       </c>
@@ -12183,7 +12188,7 @@
       </c>
     </row>
     <row r="8" spans="1:5" ht="24.95" customHeight="1">
-      <c r="A8" s="314"/>
+      <c r="A8" s="317"/>
       <c r="B8" s="65" t="s">
         <v>25</v>
       </c>
@@ -12199,7 +12204,7 @@
       </c>
     </row>
     <row r="9" spans="1:5" ht="24.95" customHeight="1">
-      <c r="A9" s="314"/>
+      <c r="A9" s="317"/>
       <c r="B9" s="65" t="s">
         <v>46</v>
       </c>
@@ -12215,7 +12220,7 @@
       </c>
     </row>
     <row r="10" spans="1:5" ht="24.95" customHeight="1">
-      <c r="A10" s="314"/>
+      <c r="A10" s="317"/>
       <c r="B10" s="65" t="s">
         <v>47</v>
       </c>
@@ -12231,7 +12236,7 @@
       </c>
     </row>
     <row r="11" spans="1:5" ht="24.95" customHeight="1">
-      <c r="A11" s="314"/>
+      <c r="A11" s="317"/>
       <c r="B11" s="65" t="s">
         <v>26</v>
       </c>
@@ -12247,7 +12252,7 @@
       </c>
     </row>
     <row r="12" spans="1:5" ht="24.95" customHeight="1">
-      <c r="A12" s="314"/>
+      <c r="A12" s="317"/>
       <c r="B12" s="65" t="s">
         <v>27</v>
       </c>
@@ -12263,7 +12268,7 @@
       </c>
     </row>
     <row r="13" spans="1:5" ht="24.95" customHeight="1">
-      <c r="A13" s="314" t="s">
+      <c r="A13" s="317" t="s">
         <v>38</v>
       </c>
       <c r="B13" s="65" t="s">
@@ -12281,7 +12286,7 @@
       </c>
     </row>
     <row r="14" spans="1:5" ht="24.95" customHeight="1">
-      <c r="A14" s="314"/>
+      <c r="A14" s="317"/>
       <c r="B14" s="65" t="s">
         <v>29</v>
       </c>
@@ -12297,7 +12302,7 @@
       </c>
     </row>
     <row r="15" spans="1:5" ht="24.95" customHeight="1">
-      <c r="A15" s="314" t="s">
+      <c r="A15" s="317" t="s">
         <v>30</v>
       </c>
       <c r="B15" s="65" t="s">
@@ -12315,7 +12320,7 @@
       </c>
     </row>
     <row r="16" spans="1:5" ht="24.95" customHeight="1">
-      <c r="A16" s="314"/>
+      <c r="A16" s="317"/>
       <c r="B16" s="65" t="s">
         <v>31</v>
       </c>
@@ -12331,14 +12336,14 @@
       </c>
     </row>
     <row r="17" spans="1:5" ht="24.95" customHeight="1">
-      <c r="A17" s="314" t="s">
+      <c r="A17" s="317" t="s">
         <v>32</v>
       </c>
-      <c r="B17" s="315"/>
+      <c r="B17" s="318"/>
       <c r="C17" s="84" t="s">
         <v>225</v>
       </c>
-      <c r="D17" s="320" t="s">
+      <c r="D17" s="323" t="s">
         <v>98</v>
       </c>
       <c r="E17" s="66" t="str">
@@ -12347,7 +12352,7 @@
       </c>
     </row>
     <row r="18" spans="1:5" ht="24.95" customHeight="1">
-      <c r="A18" s="314" t="s">
+      <c r="A18" s="317" t="s">
         <v>39</v>
       </c>
       <c r="B18" s="65" t="s">
@@ -12356,42 +12361,42 @@
       <c r="C18" s="84" t="s">
         <v>226</v>
       </c>
-      <c r="D18" s="320"/>
+      <c r="D18" s="323"/>
       <c r="E18" s="66" t="str">
         <f t="shared" ref="E18:E22" si="0">C18</f>
         <v>{급수펌프, 급탕탱크}</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="24.95" customHeight="1">
-      <c r="A19" s="314"/>
+      <c r="A19" s="317"/>
       <c r="B19" s="65" t="s">
         <v>33</v>
       </c>
       <c r="C19" s="84" t="s">
         <v>227</v>
       </c>
-      <c r="D19" s="320"/>
+      <c r="D19" s="323"/>
       <c r="E19" s="66" t="str">
         <f t="shared" si="0"/>
         <v>{고·저수조}</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="24.95" customHeight="1">
-      <c r="A20" s="314" t="s">
+      <c r="A20" s="317" t="s">
         <v>90</v>
       </c>
-      <c r="B20" s="315"/>
+      <c r="B20" s="318"/>
       <c r="C20" s="84" t="s">
         <v>228</v>
       </c>
-      <c r="D20" s="320"/>
+      <c r="D20" s="323"/>
       <c r="E20" s="66" t="str">
         <f t="shared" si="0"/>
         <v>{오·배수 통기 및 우수배수시설}</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="24.95" customHeight="1">
-      <c r="A21" s="319" t="s">
+      <c r="A21" s="322" t="s">
         <v>41</v>
       </c>
       <c r="B21" s="65" t="s">
@@ -12400,104 +12405,104 @@
       <c r="C21" s="84" t="s">
         <v>229</v>
       </c>
-      <c r="D21" s="320"/>
+      <c r="D21" s="323"/>
       <c r="E21" s="66" t="str">
         <f t="shared" si="0"/>
         <v>{오수정화설비}</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="24.95" customHeight="1">
-      <c r="A22" s="314"/>
+      <c r="A22" s="317"/>
       <c r="B22" s="65" t="s">
         <v>35</v>
       </c>
       <c r="C22" s="84" t="s">
         <v>230</v>
       </c>
-      <c r="D22" s="320"/>
+      <c r="D22" s="323"/>
       <c r="E22" s="66" t="str">
         <f t="shared" si="0"/>
         <v>{물 재이용설비}</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="24.95" customHeight="1">
-      <c r="A23" s="314" t="s">
+      <c r="A23" s="317" t="s">
         <v>42</v>
       </c>
-      <c r="B23" s="315"/>
+      <c r="B23" s="318"/>
       <c r="C23" s="84" t="s">
         <v>231</v>
       </c>
-      <c r="D23" s="320"/>
+      <c r="D23" s="323"/>
       <c r="E23" s="66" t="str">
         <f>C23</f>
         <v>{배관설비}</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="24.95" customHeight="1">
-      <c r="A24" s="314" t="s">
+      <c r="A24" s="317" t="s">
         <v>43</v>
       </c>
-      <c r="B24" s="315"/>
+      <c r="B24" s="318"/>
       <c r="C24" s="84" t="s">
         <v>232</v>
       </c>
-      <c r="D24" s="320"/>
+      <c r="D24" s="323"/>
       <c r="E24" s="66" t="str">
         <f t="shared" ref="E24:E27" si="1">C24</f>
         <v>{덕트설비}</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="24.95" customHeight="1">
-      <c r="A25" s="314" t="s">
+      <c r="A25" s="317" t="s">
         <v>44</v>
       </c>
-      <c r="B25" s="315"/>
+      <c r="B25" s="318"/>
       <c r="C25" s="84" t="s">
         <v>233</v>
       </c>
-      <c r="D25" s="320"/>
+      <c r="D25" s="323"/>
       <c r="E25" s="66" t="str">
         <f t="shared" si="1"/>
         <v>{보온설비}</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="24.95" customHeight="1">
-      <c r="A26" s="314" t="s">
+      <c r="A26" s="317" t="s">
         <v>36</v>
       </c>
-      <c r="B26" s="315"/>
+      <c r="B26" s="318"/>
       <c r="C26" s="84" t="s">
         <v>234</v>
       </c>
-      <c r="D26" s="320"/>
+      <c r="D26" s="323"/>
       <c r="E26" s="66" t="str">
         <f t="shared" si="1"/>
         <v>{자동제어설비}</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="24.95" customHeight="1">
-      <c r="A27" s="314" t="s">
+      <c r="A27" s="317" t="s">
         <v>45</v>
       </c>
-      <c r="B27" s="315"/>
+      <c r="B27" s="318"/>
       <c r="C27" s="84" t="s">
         <v>235</v>
       </c>
-      <c r="D27" s="320"/>
+      <c r="D27" s="323"/>
       <c r="E27" s="66" t="str">
         <f t="shared" si="1"/>
         <v>{방음·방진·내진 설비}</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="49.5" customHeight="1">
-      <c r="A28" s="318" t="s">
+      <c r="A28" s="321" t="s">
         <v>51</v>
       </c>
-      <c r="B28" s="318"/>
-      <c r="C28" s="318"/>
-      <c r="D28" s="318"/>
-      <c r="E28" s="318"/>
+      <c r="B28" s="321"/>
+      <c r="C28" s="321"/>
+      <c r="D28" s="321"/>
+      <c r="E28" s="321"/>
     </row>
     <row r="29" spans="1:5" ht="18.75" customHeight="1">
       <c r="B29" s="10"/>
@@ -12519,11 +12524,6 @@
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A3:A12"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="A15:A16"/>
-    <mergeCell ref="A17:B17"/>
     <mergeCell ref="A18:A19"/>
     <mergeCell ref="A27:B27"/>
     <mergeCell ref="A2:B2"/>
@@ -12535,11 +12535,16 @@
     <mergeCell ref="A25:B25"/>
     <mergeCell ref="A26:B26"/>
     <mergeCell ref="D17:D27"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A3:A12"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="A15:A16"/>
+    <mergeCell ref="A17:B17"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.35433070866141736" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="9" scale="90" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" fitToHeight="0" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>
@@ -12558,20 +12563,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="29.25" customHeight="1" thickBot="1">
-      <c r="A1" s="330" t="s">
+      <c r="A1" s="324" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="330"/>
-      <c r="C1" s="330"/>
-      <c r="D1" s="330"/>
-      <c r="E1" s="330"/>
-      <c r="F1" s="330"/>
+      <c r="B1" s="324"/>
+      <c r="C1" s="324"/>
+      <c r="D1" s="324"/>
+      <c r="E1" s="324"/>
+      <c r="F1" s="324"/>
     </row>
     <row r="2" spans="1:6" ht="24" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A2" s="316" t="s">
+      <c r="A2" s="319" t="s">
         <v>48</v>
       </c>
-      <c r="B2" s="317"/>
+      <c r="B2" s="320"/>
       <c r="C2" s="80" t="s">
         <v>50</v>
       </c>
@@ -12586,10 +12591,10 @@
       </c>
     </row>
     <row r="3" spans="1:6" ht="21.95" customHeight="1" thickTop="1">
-      <c r="A3" s="322" t="s">
+      <c r="A3" s="316" t="s">
         <v>55</v>
       </c>
-      <c r="B3" s="331"/>
+      <c r="B3" s="325"/>
       <c r="C3" s="77">
         <v>1</v>
       </c>
@@ -12605,10 +12610,10 @@
       </c>
     </row>
     <row r="4" spans="1:6" ht="21.95" customHeight="1">
-      <c r="A4" s="314" t="s">
+      <c r="A4" s="317" t="s">
         <v>56</v>
       </c>
-      <c r="B4" s="315"/>
+      <c r="B4" s="318"/>
       <c r="C4" s="64">
         <v>1</v>
       </c>
@@ -12624,7 +12629,7 @@
       </c>
     </row>
     <row r="5" spans="1:6" ht="21.95" customHeight="1">
-      <c r="A5" s="314" t="s">
+      <c r="A5" s="317" t="s">
         <v>37</v>
       </c>
       <c r="B5" s="65" t="s">
@@ -12647,7 +12652,7 @@
       </c>
     </row>
     <row r="6" spans="1:6" ht="21.95" customHeight="1">
-      <c r="A6" s="314"/>
+      <c r="A6" s="317"/>
       <c r="B6" s="65" t="s">
         <v>22</v>
       </c>
@@ -12668,7 +12673,7 @@
       </c>
     </row>
     <row r="7" spans="1:6" ht="21.95" customHeight="1">
-      <c r="A7" s="314"/>
+      <c r="A7" s="317"/>
       <c r="B7" s="65" t="s">
         <v>86</v>
       </c>
@@ -12690,7 +12695,7 @@
       </c>
     </row>
     <row r="8" spans="1:6" ht="21.95" customHeight="1">
-      <c r="A8" s="314"/>
+      <c r="A8" s="317"/>
       <c r="B8" s="65" t="s">
         <v>23</v>
       </c>
@@ -12711,7 +12716,7 @@
       </c>
     </row>
     <row r="9" spans="1:6" ht="21.95" customHeight="1">
-      <c r="A9" s="314"/>
+      <c r="A9" s="317"/>
       <c r="B9" s="65" t="s">
         <v>24</v>
       </c>
@@ -12732,7 +12737,7 @@
       </c>
     </row>
     <row r="10" spans="1:6" ht="21.95" customHeight="1">
-      <c r="A10" s="314"/>
+      <c r="A10" s="317"/>
       <c r="B10" s="65" t="s">
         <v>25</v>
       </c>
@@ -12753,7 +12758,7 @@
       </c>
     </row>
     <row r="11" spans="1:6" ht="21.95" customHeight="1">
-      <c r="A11" s="314"/>
+      <c r="A11" s="317"/>
       <c r="B11" s="65" t="s">
         <v>46</v>
       </c>
@@ -12774,7 +12779,7 @@
       </c>
     </row>
     <row r="12" spans="1:6" ht="21.95" customHeight="1">
-      <c r="A12" s="314"/>
+      <c r="A12" s="317"/>
       <c r="B12" s="65" t="s">
         <v>47</v>
       </c>
@@ -12795,7 +12800,7 @@
       </c>
     </row>
     <row r="13" spans="1:6" ht="21.95" customHeight="1">
-      <c r="A13" s="314"/>
+      <c r="A13" s="317"/>
       <c r="B13" s="65" t="s">
         <v>26</v>
       </c>
@@ -12816,7 +12821,7 @@
       </c>
     </row>
     <row r="14" spans="1:6" ht="21.95" customHeight="1">
-      <c r="A14" s="314"/>
+      <c r="A14" s="317"/>
       <c r="B14" s="65" t="s">
         <v>27</v>
       </c>
@@ -12837,7 +12842,7 @@
       </c>
     </row>
     <row r="15" spans="1:6" ht="21.95" customHeight="1">
-      <c r="A15" s="314" t="s">
+      <c r="A15" s="317" t="s">
         <v>38</v>
       </c>
       <c r="B15" s="65" t="s">
@@ -12860,7 +12865,7 @@
       </c>
     </row>
     <row r="16" spans="1:6" ht="21.95" customHeight="1">
-      <c r="A16" s="314"/>
+      <c r="A16" s="317"/>
       <c r="B16" s="65" t="s">
         <v>29</v>
       </c>
@@ -12881,7 +12886,7 @@
       </c>
     </row>
     <row r="17" spans="1:6" ht="21.95" customHeight="1">
-      <c r="A17" s="314" t="s">
+      <c r="A17" s="317" t="s">
         <v>30</v>
       </c>
       <c r="B17" s="65" t="s">
@@ -12904,7 +12909,7 @@
       </c>
     </row>
     <row r="18" spans="1:6" ht="21.95" customHeight="1">
-      <c r="A18" s="314"/>
+      <c r="A18" s="317"/>
       <c r="B18" s="65" t="s">
         <v>31</v>
       </c>
@@ -12925,10 +12930,10 @@
       </c>
     </row>
     <row r="19" spans="1:6" ht="21.95" customHeight="1">
-      <c r="A19" s="314" t="s">
+      <c r="A19" s="317" t="s">
         <v>32</v>
       </c>
-      <c r="B19" s="315"/>
+      <c r="B19" s="318"/>
       <c r="C19" s="65">
         <v>1</v>
       </c>
@@ -12946,7 +12951,7 @@
       </c>
     </row>
     <row r="20" spans="1:6" ht="21.95" customHeight="1">
-      <c r="A20" s="314" t="s">
+      <c r="A20" s="317" t="s">
         <v>39</v>
       </c>
       <c r="B20" s="65" t="s">
@@ -12969,7 +12974,7 @@
       </c>
     </row>
     <row r="21" spans="1:6" ht="21.95" customHeight="1">
-      <c r="A21" s="314"/>
+      <c r="A21" s="317"/>
       <c r="B21" s="65" t="s">
         <v>33</v>
       </c>
@@ -12990,10 +12995,10 @@
       </c>
     </row>
     <row r="22" spans="1:6" ht="21.95" customHeight="1">
-      <c r="A22" s="314" t="s">
+      <c r="A22" s="317" t="s">
         <v>40</v>
       </c>
-      <c r="B22" s="315"/>
+      <c r="B22" s="318"/>
       <c r="C22" s="65">
         <v>1</v>
       </c>
@@ -13011,7 +13016,7 @@
       </c>
     </row>
     <row r="23" spans="1:6" ht="21.95" customHeight="1">
-      <c r="A23" s="319" t="s">
+      <c r="A23" s="322" t="s">
         <v>41</v>
       </c>
       <c r="B23" s="65" t="s">
@@ -13034,7 +13039,7 @@
       </c>
     </row>
     <row r="24" spans="1:6" ht="21.95" customHeight="1">
-      <c r="A24" s="314"/>
+      <c r="A24" s="317"/>
       <c r="B24" s="65" t="s">
         <v>35</v>
       </c>
@@ -13055,10 +13060,10 @@
       </c>
     </row>
     <row r="25" spans="1:6" ht="21.95" customHeight="1">
-      <c r="A25" s="314" t="s">
+      <c r="A25" s="317" t="s">
         <v>42</v>
       </c>
-      <c r="B25" s="315"/>
+      <c r="B25" s="318"/>
       <c r="C25" s="65">
         <v>1</v>
       </c>
@@ -13076,10 +13081,10 @@
       </c>
     </row>
     <row r="26" spans="1:6" ht="21.95" customHeight="1">
-      <c r="A26" s="314" t="s">
+      <c r="A26" s="317" t="s">
         <v>43</v>
       </c>
-      <c r="B26" s="315"/>
+      <c r="B26" s="318"/>
       <c r="C26" s="65">
         <v>1</v>
       </c>
@@ -13097,10 +13102,10 @@
       </c>
     </row>
     <row r="27" spans="1:6" ht="21.95" customHeight="1">
-      <c r="A27" s="314" t="s">
+      <c r="A27" s="317" t="s">
         <v>44</v>
       </c>
-      <c r="B27" s="315"/>
+      <c r="B27" s="318"/>
       <c r="C27" s="65">
         <v>1</v>
       </c>
@@ -13118,10 +13123,10 @@
       </c>
     </row>
     <row r="28" spans="1:6" ht="21.95" customHeight="1">
-      <c r="A28" s="314" t="s">
+      <c r="A28" s="317" t="s">
         <v>36</v>
       </c>
-      <c r="B28" s="315"/>
+      <c r="B28" s="318"/>
       <c r="C28" s="65">
         <v>1</v>
       </c>
@@ -13139,10 +13144,10 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="21.95" customHeight="1">
-      <c r="A29" s="314" t="s">
+      <c r="A29" s="317" t="s">
         <v>45</v>
       </c>
-      <c r="B29" s="315"/>
+      <c r="B29" s="318"/>
       <c r="C29" s="65">
         <v>1</v>
       </c>
@@ -13160,10 +13165,10 @@
       </c>
     </row>
     <row r="30" spans="1:6" ht="21.95" customHeight="1">
-      <c r="A30" s="314" t="s">
+      <c r="A30" s="317" t="s">
         <v>57</v>
       </c>
-      <c r="B30" s="315"/>
+      <c r="B30" s="318"/>
       <c r="C30" s="65">
         <v>1</v>
       </c>
@@ -13181,10 +13186,10 @@
       </c>
     </row>
     <row r="31" spans="1:6" ht="21.95" customHeight="1">
-      <c r="A31" s="314" t="s">
+      <c r="A31" s="317" t="s">
         <v>58</v>
       </c>
-      <c r="B31" s="315"/>
+      <c r="B31" s="318"/>
       <c r="C31" s="65"/>
       <c r="D31" s="65">
         <f>SUM(D19:D30)</f>
@@ -13200,10 +13205,10 @@
       </c>
     </row>
     <row r="32" spans="1:6" ht="21.95" customHeight="1">
-      <c r="A32" s="314" t="s">
+      <c r="A32" s="317" t="s">
         <v>59</v>
       </c>
-      <c r="B32" s="315"/>
+      <c r="B32" s="318"/>
       <c r="C32" s="65"/>
       <c r="D32" s="65">
         <f>SUM(D5:D18)</f>
@@ -13219,10 +13224,10 @@
       </c>
     </row>
     <row r="33" spans="1:6" ht="21.95" customHeight="1">
-      <c r="A33" s="328" t="s">
+      <c r="A33" s="331" t="s">
         <v>60</v>
       </c>
-      <c r="B33" s="329"/>
+      <c r="B33" s="332"/>
       <c r="C33" s="74"/>
       <c r="D33" s="74">
         <f>ROUNDDOWN(SUM(D31:D32,D3:D4),0)</f>
@@ -13238,7 +13243,7 @@
       </c>
     </row>
     <row r="34" spans="1:6" ht="25.5" customHeight="1">
-      <c r="A34" s="323" t="s">
+      <c r="A34" s="326" t="s">
         <v>158</v>
       </c>
       <c r="B34" s="71" t="s">
@@ -13258,7 +13263,7 @@
       </c>
     </row>
     <row r="35" spans="1:6" ht="25.5" customHeight="1">
-      <c r="A35" s="324"/>
+      <c r="A35" s="327"/>
       <c r="B35" s="75" t="s">
         <v>156</v>
       </c>
@@ -13279,23 +13284,37 @@
       </c>
     </row>
     <row r="36" spans="1:6" ht="25.5" customHeight="1" thickBot="1">
-      <c r="A36" s="325"/>
+      <c r="A36" s="328"/>
       <c r="B36" s="85" t="s">
         <v>170</v>
       </c>
       <c r="C36" s="86" t="s">
         <v>154</v>
       </c>
-      <c r="D36" s="326">
+      <c r="D36" s="329">
         <f>SUM(D35:F35)</f>
         <v>9660000</v>
       </c>
-      <c r="E36" s="327"/>
-      <c r="F36" s="327"/>
+      <c r="E36" s="330"/>
+      <c r="F36" s="330"/>
     </row>
     <row r="37" spans="1:6" ht="14.25" thickTop="1"/>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="A34:A36"/>
+    <mergeCell ref="D36:F36"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="A27:B27"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A4:B4"/>
@@ -13304,20 +13323,6 @@
     <mergeCell ref="A5:A14"/>
     <mergeCell ref="A15:A16"/>
     <mergeCell ref="A17:A18"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="A34:A36"/>
-    <mergeCell ref="D36:F36"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="A31:B31"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
@@ -13340,28 +13345,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="24" customHeight="1">
-      <c r="A1" s="332" t="s">
+      <c r="A1" s="333" t="s">
         <v>61</v>
       </c>
-      <c r="B1" s="332"/>
-      <c r="C1" s="332"/>
-      <c r="D1" s="332"/>
-      <c r="E1" s="332"/>
-      <c r="F1" s="332"/>
+      <c r="B1" s="333"/>
+      <c r="C1" s="333"/>
+      <c r="D1" s="333"/>
+      <c r="E1" s="333"/>
+      <c r="F1" s="333"/>
     </row>
     <row r="2" spans="1:6" ht="27" customHeight="1">
-      <c r="A2" s="333" t="s">
+      <c r="A2" s="334" t="s">
         <v>62</v>
       </c>
-      <c r="B2" s="334"/>
-      <c r="C2" s="333" t="s">
+      <c r="B2" s="335"/>
+      <c r="C2" s="334" t="s">
         <v>63</v>
       </c>
-      <c r="D2" s="334"/>
-      <c r="E2" s="333" t="s">
+      <c r="D2" s="335"/>
+      <c r="E2" s="334" t="s">
         <v>64</v>
       </c>
-      <c r="F2" s="334"/>
+      <c r="F2" s="335"/>
     </row>
     <row r="3" spans="1:6" ht="27" customHeight="1">
       <c r="A3" s="3" t="s">
@@ -13464,16 +13469,16 @@
       </c>
     </row>
     <row r="8" spans="1:6" ht="27" customHeight="1">
-      <c r="A8" s="335" t="s">
+      <c r="A8" s="336" t="s">
         <v>73</v>
       </c>
-      <c r="B8" s="337">
+      <c r="B8" s="338">
         <v>2</v>
       </c>
-      <c r="C8" s="335" t="s">
+      <c r="C8" s="336" t="s">
         <v>78</v>
       </c>
-      <c r="D8" s="337">
+      <c r="D8" s="338">
         <v>1.4</v>
       </c>
       <c r="E8" s="1" t="s">
@@ -13484,10 +13489,10 @@
       </c>
     </row>
     <row r="9" spans="1:6" ht="27" customHeight="1">
-      <c r="A9" s="336"/>
-      <c r="B9" s="338"/>
-      <c r="C9" s="336"/>
-      <c r="D9" s="338"/>
+      <c r="A9" s="337"/>
+      <c r="B9" s="339"/>
+      <c r="C9" s="337"/>
+      <c r="D9" s="339"/>
       <c r="E9" s="3" t="s">
         <v>84</v>
       </c>
